--- a/database/event/3714/event_3714_evp_summary.xlsx
+++ b/database/event/3714/event_3714_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.0605</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3298</v>
+        <v>2.2693</v>
       </c>
       <c r="E2" t="n">
         <v>6.8102</v>
@@ -548,7 +548,7 @@
         <v>0.972</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1001</v>
+        <v>2.0428</v>
       </c>
       <c r="E3" t="n">
         <v>6.2417</v>
@@ -594,7 +594,7 @@
         <v>0.8609</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8121</v>
+        <v>1.7587</v>
       </c>
       <c r="E4" t="n">
         <v>5.5286</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5526</v>
+        <v>4.5399</v>
       </c>
       <c r="C5" t="n">
-        <v>0.709</v>
+        <v>0.707</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4178</v>
+        <v>1.3648</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5526</v>
+        <v>4.5399</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3887</v>
+        <v>3.376</v>
       </c>
       <c r="G5" t="n">
         <v>1.1639</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3887</v>
+        <v>3.376</v>
       </c>
       <c r="I5" t="n">
         <v>3.4044</v>
@@ -686,7 +686,7 @@
         <v>0.6807</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3445</v>
+        <v>1.2975</v>
       </c>
       <c r="E6" t="n">
         <v>4.3711</v>
@@ -732,7 +732,7 @@
         <v>0.5829</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0907</v>
+        <v>1.0473</v>
       </c>
       <c r="E7" t="n">
         <v>3.7429</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0516</v>
+        <v>3.043</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4752</v>
+        <v>0.4739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8114</v>
+        <v>0.7684</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0516</v>
+        <v>3.043</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3025</v>
+        <v>2.2939</v>
       </c>
       <c r="G8" t="n">
         <v>0.7491</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3025</v>
+        <v>2.2939</v>
       </c>
       <c r="I8" t="n">
         <v>2.3132</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9866</v>
+        <v>2.9796</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4651</v>
+        <v>0.464</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7852</v>
+        <v>0.7432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9866</v>
+        <v>2.9796</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8627</v>
+        <v>1.8557</v>
       </c>
       <c r="G9" t="n">
         <v>1.1239</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8627</v>
+        <v>1.8557</v>
       </c>
       <c r="I9" t="n">
         <v>1.8713</v>
@@ -870,7 +870,7 @@
         <v>0.4034</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6251</v>
+        <v>0.5881</v>
       </c>
       <c r="E10" t="n">
         <v>2.5905</v>
@@ -916,7 +916,7 @@
         <v>0.402</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6214</v>
+        <v>0.5844</v>
       </c>
       <c r="E11" t="n">
         <v>2.5812</v>
@@ -962,7 +962,7 @@
         <v>0.3904</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5915</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2.5071</v>
@@ -1008,7 +1008,7 @@
         <v>0.3824</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5708</v>
+        <v>0.5345</v>
       </c>
       <c r="E13" t="n">
         <v>2.4559</v>
@@ -1054,7 +1054,7 @@
         <v>0.3388</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4575</v>
+        <v>0.4228</v>
       </c>
       <c r="E14" t="n">
         <v>2.1756</v>
@@ -1100,7 +1100,7 @@
         <v>0.2598</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2527</v>
+        <v>0.2208</v>
       </c>
       <c r="E15" t="n">
         <v>1.6685</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.619</v>
+        <v>1.6123</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2521</v>
+        <v>0.2511</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2327</v>
+        <v>0.1984</v>
       </c>
       <c r="E16" t="n">
-        <v>1.619</v>
+        <v>1.6123</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8041</v>
+        <v>1.7974</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1851</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8041</v>
+        <v>1.7974</v>
       </c>
       <c r="I16" t="n">
         <v>1.8125</v>
@@ -1192,7 +1192,7 @@
         <v>0.2165</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1404</v>
+        <v>0.1101</v>
       </c>
       <c r="E17" t="n">
         <v>1.3905</v>
@@ -1238,7 +1238,7 @@
         <v>0.2114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1271</v>
+        <v>0.097</v>
       </c>
       <c r="E18" t="n">
         <v>1.3577</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3242</v>
+        <v>1.3212</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2062</v>
+        <v>0.2057</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1136</v>
+        <v>0.0825</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3242</v>
+        <v>1.3212</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8043</v>
+        <v>0.8013</v>
       </c>
       <c r="G19" t="n">
         <v>0.5199</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8043</v>
+        <v>0.8013</v>
       </c>
       <c r="I19" t="n">
         <v>0.8080000000000001</v>
@@ -1330,7 +1330,7 @@
         <v>0.1864</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0621</v>
+        <v>0.0329</v>
       </c>
       <c r="E20" t="n">
         <v>1.1967</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1738</v>
+        <v>1.1728</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1828</v>
+        <v>0.1826</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0528</v>
+        <v>0.0233</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1738</v>
+        <v>1.1728</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2634</v>
+        <v>0.2624</v>
       </c>
       <c r="G21" t="n">
         <v>0.9104</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2634</v>
+        <v>0.2624</v>
       </c>
       <c r="I21" t="n">
         <v>0.2646</v>
@@ -1422,7 +1422,7 @@
         <v>0.1201</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1098</v>
+        <v>-0.1366</v>
       </c>
       <c r="E22" t="n">
         <v>0.7713</v>
@@ -1468,7 +1468,7 @@
         <v>0.11</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1361</v>
+        <v>-0.1626</v>
       </c>
       <c r="E23" t="n">
         <v>0.7060999999999999</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.606</v>
+        <v>0.6015</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0944</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1766</v>
+        <v>-0.2043</v>
       </c>
       <c r="E24" t="n">
-        <v>0.606</v>
+        <v>0.6015</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5979</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="I24" t="n">
         <v>1.2095</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5476</v>
+        <v>0.5462</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0853</v>
+        <v>0.0851</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2001</v>
+        <v>-0.2263</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5476</v>
+        <v>0.5462</v>
       </c>
       <c r="F25" t="n">
-        <v>0.371</v>
+        <v>0.3696</v>
       </c>
       <c r="G25" t="n">
         <v>0.1766</v>
       </c>
       <c r="H25" t="n">
-        <v>0.371</v>
+        <v>0.3696</v>
       </c>
       <c r="I25" t="n">
         <v>0.3727</v>
@@ -1606,7 +1606,7 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2199</v>
+        <v>-0.2452</v>
       </c>
       <c r="E26" t="n">
         <v>0.4987</v>
@@ -1652,7 +1652,7 @@
         <v>0.0255</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3553</v>
+        <v>-0.3787</v>
       </c>
       <c r="E27" t="n">
         <v>0.1636</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0173</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4662</v>
+        <v>-0.4881</v>
       </c>
       <c r="E28" t="n">
         <v>-0.111</v>
@@ -1744,7 +1744,7 @@
         <v>-0.047</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5434</v>
+        <v>-0.5642</v>
       </c>
       <c r="E29" t="n">
         <v>-0.302</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0549</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5638</v>
+        <v>-0.5843</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3525</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0801</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6292</v>
+        <v>-0.6489</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5145999999999999</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.54</v>
+        <v>-0.5373</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0837</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6395</v>
+        <v>-0.658</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.54</v>
+        <v>-0.5373</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7144</v>
+        <v>-0.7117</v>
       </c>
       <c r="G32" t="n">
         <v>0.1744</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7144</v>
+        <v>-0.7117</v>
       </c>
       <c r="I32" t="n">
         <v>-0.7177</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0983</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6763</v>
+        <v>-0.6953</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6311</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1047</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.7118</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6724</v>
@@ -2020,7 +2020,7 @@
         <v>-0.138</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7793</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8861</v>
@@ -2066,7 +2066,7 @@
         <v>-0.152</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8156</v>
+        <v>-0.8327</v>
       </c>
       <c r="E36" t="n">
         <v>-0.976</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2133</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9748</v>
+        <v>-0.9897</v>
       </c>
       <c r="E37" t="n">
         <v>-1.37</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2203</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9928</v>
+        <v>-1.0074</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4145</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2244</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0034</v>
+        <v>-1.0179</v>
       </c>
       <c r="E39" t="n">
         <v>-1.4408</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3114</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0397</v>
+        <v>-3.0346</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4734</v>
+        <v>-0.4726</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6493</v>
+        <v>-1.6529</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0397</v>
+        <v>-3.0346</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3603</v>
+        <v>-1.3552</v>
       </c>
       <c r="G41" t="n">
         <v>-1.6794</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3603</v>
+        <v>-1.3552</v>
       </c>
       <c r="I41" t="n">
         <v>-1.3666</v>

--- a/database/event/3714/event_3714_evp_summary.xlsx
+++ b/database/event/3714/event_3714_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8102</v>
+        <v>5.938</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0605</v>
+        <v>0.9247</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2693</v>
+        <v>2.0427</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8102</v>
+        <v>5.938</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3505</v>
+        <v>3.0523</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4598</v>
+        <v>2.8857</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3505</v>
+        <v>5.268</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7156</v>
+        <v>2.7391</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4598</v>
+        <v>2.8857</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>114</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1754</v>
+        <v>5.6248</v>
       </c>
       <c r="N2" t="n">
         <v>255</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2417</v>
+        <v>5.8619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.972</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0428</v>
+        <v>2.0083</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2417</v>
+        <v>5.8619</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9274</v>
+        <v>3.0907</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3142</v>
+        <v>2.7713</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9274</v>
+        <v>3.4268</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9274</v>
+        <v>3.4268</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3142</v>
+        <v>2.7713</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2416</v>
+        <v>6.1981</v>
       </c>
       <c r="N3" t="n">
         <v>254</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5286</v>
+        <v>4.7977</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8609</v>
+        <v>0.7471</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7587</v>
+        <v>1.5279</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5286</v>
+        <v>4.7977</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2585</v>
+        <v>3.7371</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2701</v>
+        <v>1.0606</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5723</v>
+        <v>7.6809</v>
       </c>
       <c r="I4" t="n">
-        <v>3.706</v>
+        <v>3.9937</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2701</v>
+        <v>1.0606</v>
       </c>
       <c r="K4" t="n">
         <v>139</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9761</v>
+        <v>5.0543</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5399</v>
+        <v>4.5153</v>
       </c>
       <c r="C5" t="n">
-        <v>0.707</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3648</v>
+        <v>1.4004</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5399</v>
+        <v>4.5153</v>
       </c>
       <c r="F5" t="n">
-        <v>3.376</v>
+        <v>2.1102</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1639</v>
+        <v>2.4051</v>
       </c>
       <c r="H5" t="n">
-        <v>3.376</v>
+        <v>2.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4044</v>
+        <v>1.0972</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1639</v>
+        <v>2.4051</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5683</v>
+        <v>3.5023</v>
       </c>
       <c r="N5" t="n">
-        <v>190</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3711</v>
+        <v>4.4498</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6807</v>
+        <v>0.6929</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2975</v>
+        <v>1.3708</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3711</v>
+        <v>4.4498</v>
       </c>
       <c r="F6" t="n">
-        <v>4.24</v>
+        <v>3.4977</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1311</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4979</v>
+        <v>4.3206</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6456</v>
+        <v>4.4983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1311</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7767</v>
+        <v>5.4504</v>
       </c>
       <c r="N6" t="n">
-        <v>256</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7429</v>
+        <v>4.1413</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5829</v>
+        <v>0.6449</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0473</v>
+        <v>1.2316</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7429</v>
+        <v>4.1413</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1243</v>
+        <v>3.6633</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6186</v>
+        <v>0.478</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1243</v>
+        <v>7.421</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9113</v>
+        <v>3.8586</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6186</v>
+        <v>0.478</v>
       </c>
       <c r="K7" t="n">
         <v>139</v>
@@ -759,7 +759,7 @@
         <v>117</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5299</v>
+        <v>4.3366</v>
       </c>
       <c r="N7" t="n">
         <v>256</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.043</v>
+        <v>3.8192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4739</v>
+        <v>0.5947</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7684</v>
+        <v>1.0862</v>
       </c>
       <c r="E8" t="n">
-        <v>3.043</v>
+        <v>3.8192</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2939</v>
+        <v>2.9524</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7491</v>
+        <v>0.8668</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2939</v>
+        <v>3.1233</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3132</v>
+        <v>3.2517</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7491</v>
+        <v>0.8668</v>
       </c>
       <c r="K8" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L8" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0623</v>
+        <v>4.1185</v>
       </c>
       <c r="N8" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9796</v>
+        <v>3.086</v>
       </c>
       <c r="C9" t="n">
-        <v>0.464</v>
+        <v>0.4806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7432</v>
+        <v>0.7552</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9796</v>
+        <v>3.086</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8557</v>
+        <v>2.0756</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1239</v>
+        <v>1.0104</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8557</v>
+        <v>2.0756</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8713</v>
+        <v>2.0756</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1239</v>
+        <v>1.0104</v>
       </c>
       <c r="K9" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9952</v>
+        <v>3.086</v>
       </c>
       <c r="N9" t="n">
-        <v>190</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5905</v>
+        <v>2.9035</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4034</v>
+        <v>0.4521</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5881</v>
+        <v>0.6728</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5905</v>
+        <v>2.9035</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2947</v>
+        <v>1.7307</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2958</v>
+        <v>1.1728</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2947</v>
+        <v>1.7307</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2947</v>
+        <v>1.7307</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2958</v>
+        <v>1.1728</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5905</v>
+        <v>2.9035</v>
       </c>
       <c r="N10" t="n">
         <v>203</v>
@@ -906,173 +906,173 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5812</v>
+        <v>2.8854</v>
       </c>
       <c r="C11" t="n">
-        <v>0.402</v>
+        <v>0.4493</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5844</v>
+        <v>0.6646</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5812</v>
+        <v>2.8854</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1278</v>
+        <v>1.8604</v>
       </c>
       <c r="G11" t="n">
-        <v>3.709</v>
+        <v>1.025</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1278</v>
+        <v>1.8604</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9141</v>
+        <v>0.9673</v>
       </c>
       <c r="J11" t="n">
-        <v>3.709</v>
+        <v>1.025</v>
       </c>
       <c r="K11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L11" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7949</v>
+        <v>1.9923</v>
       </c>
       <c r="N11" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5071</v>
+        <v>2.8095</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3904</v>
+        <v>0.4375</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.6303</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5071</v>
+        <v>2.8095</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4043</v>
+        <v>3.3351</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1028</v>
+        <v>-0.5256</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4043</v>
+        <v>6.2646</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4043</v>
+        <v>3.2573</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1028</v>
+        <v>-0.5256</v>
       </c>
       <c r="K12" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="L12" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5071</v>
+        <v>2.7317</v>
       </c>
       <c r="N12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4559</v>
+        <v>2.7067</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3824</v>
+        <v>0.4215</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5345</v>
+        <v>0.5839</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4559</v>
+        <v>2.7067</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5855</v>
+        <v>2.1334</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1296</v>
+        <v>0.5733</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5855</v>
+        <v>2.1334</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9061</v>
+        <v>2.2211</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1296</v>
+        <v>0.5733</v>
       </c>
       <c r="K13" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7765</v>
+        <v>2.7944</v>
       </c>
       <c r="N13" t="n">
-        <v>255</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1756</v>
+        <v>2.666</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3388</v>
+        <v>0.4152</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4228</v>
+        <v>0.5656</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1756</v>
+        <v>2.666</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3255</v>
+        <v>2.204</v>
       </c>
       <c r="G14" t="n">
-        <v>2.501</v>
+        <v>0.462</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3255</v>
+        <v>2.2792</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2638</v>
+        <v>1.1851</v>
       </c>
       <c r="J14" t="n">
-        <v>2.501</v>
+        <v>0.462</v>
       </c>
       <c r="K14" t="n">
         <v>141</v>
@@ -1081,7 +1081,7 @@
         <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2372</v>
+        <v>1.6471</v>
       </c>
       <c r="N14" t="n">
         <v>255</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6685</v>
+        <v>2.5015</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2598</v>
+        <v>0.3895</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2208</v>
+        <v>0.4913</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6685</v>
+        <v>2.5015</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7104</v>
+        <v>0.4083</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9581</v>
+        <v>2.0932</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7104</v>
+        <v>0.4083</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5758</v>
+        <v>0.2123</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9581</v>
+        <v>2.0932</v>
       </c>
       <c r="K15" t="n">
         <v>141</v>
@@ -1127,7 +1127,7 @@
         <v>114</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5339</v>
+        <v>2.3055</v>
       </c>
       <c r="N15" t="n">
         <v>255</v>
@@ -1136,403 +1136,403 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6123</v>
+        <v>2.3649</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2511</v>
+        <v>0.3683</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1984</v>
+        <v>0.4296</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6123</v>
+        <v>2.3649</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7974</v>
+        <v>1.9556</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1851</v>
+        <v>0.4093</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7974</v>
+        <v>1.9556</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8125</v>
+        <v>2.036</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1851</v>
+        <v>0.4093</v>
       </c>
       <c r="K16" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L16" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6274</v>
+        <v>2.4453</v>
       </c>
       <c r="N16" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3905</v>
+        <v>2.2637</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2165</v>
+        <v>0.3525</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1101</v>
+        <v>0.3839</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3905</v>
+        <v>2.2637</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9952</v>
+        <v>-1.0336</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6047</v>
+        <v>3.2973</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9952</v>
+        <v>-1.0336</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9952</v>
+        <v>-0.5374</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6047</v>
+        <v>3.2973</v>
       </c>
       <c r="K17" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L17" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3905</v>
+        <v>2.7599</v>
       </c>
       <c r="N17" t="n">
-        <v>203</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3577</v>
+        <v>2.1695</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2114</v>
+        <v>0.3378</v>
       </c>
       <c r="D18" t="n">
-        <v>0.097</v>
+        <v>0.3414</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3577</v>
+        <v>2.1695</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2396</v>
+        <v>2.4949</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1181</v>
+        <v>-0.3254</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2396</v>
+        <v>2.4949</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0047</v>
+        <v>2.4949</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1181</v>
+        <v>-0.3254</v>
       </c>
       <c r="K18" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L18" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1228</v>
+        <v>2.1695</v>
       </c>
       <c r="N18" t="n">
-        <v>255</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3212</v>
+        <v>1.8241</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2057</v>
+        <v>0.2841</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0825</v>
+        <v>0.1855</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3212</v>
+        <v>1.8241</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8013</v>
+        <v>1.4703</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5199</v>
+        <v>0.3538</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8013</v>
+        <v>1.4703</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8080000000000001</v>
+        <v>1.4703</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5199</v>
+        <v>0.3538</v>
       </c>
       <c r="K19" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="L19" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3279</v>
+        <v>1.8241</v>
       </c>
       <c r="N19" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1967</v>
+        <v>1.812</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1864</v>
+        <v>0.2822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0329</v>
+        <v>0.18</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1967</v>
+        <v>1.812</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9673</v>
+        <v>1.8568</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2294</v>
+        <v>-0.0448</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9673</v>
+        <v>1.8568</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9673</v>
+        <v>1.9332</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2294</v>
+        <v>-0.0448</v>
       </c>
       <c r="K20" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="L20" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1967</v>
+        <v>1.8884</v>
       </c>
       <c r="N20" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1728</v>
+        <v>1.3931</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1826</v>
+        <v>0.2169</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0233</v>
+        <v>-0.0091</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1728</v>
+        <v>1.3931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2624</v>
+        <v>1.9547</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9104</v>
+        <v>-0.5616</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2624</v>
+        <v>1.9547</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2646</v>
+        <v>1.9547</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9104</v>
+        <v>-0.5616</v>
       </c>
       <c r="K21" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="M21" t="n">
-        <v>1.175</v>
+        <v>1.3931</v>
       </c>
       <c r="N21" t="n">
-        <v>274</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>glow</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7713</v>
+        <v>1.1861</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1201</v>
+        <v>0.1847</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1366</v>
+        <v>-0.1025</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7713</v>
+        <v>1.1861</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7713</v>
+        <v>1.4637</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.2776</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7713</v>
+        <v>1.4637</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7713</v>
+        <v>1.4637</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.2776</v>
       </c>
       <c r="K22" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7713</v>
+        <v>1.1861</v>
       </c>
       <c r="N22" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.1777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.11</v>
+        <v>0.1834</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1626</v>
+        <v>-0.1063</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.1777</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6056</v>
+        <v>0.4603</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8995</v>
+        <v>0.7174</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6056</v>
+        <v>0.4603</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6056</v>
+        <v>0.4792</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8995</v>
+        <v>0.7174</v>
       </c>
       <c r="K23" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="L23" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.1966</v>
       </c>
       <c r="N23" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6015</v>
+        <v>1.0792</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1681</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2043</v>
+        <v>-0.1508</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6015</v>
+        <v>1.0792</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1994</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5979</v>
+        <v>0.3287</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1994</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2095</v>
+        <v>0.7814</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5979</v>
+        <v>0.3287</v>
       </c>
       <c r="K24" t="n">
         <v>114</v>
@@ -1541,7 +1541,7 @@
         <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6116</v>
+        <v>1.1101</v>
       </c>
       <c r="N24" t="n">
         <v>190</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5462</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0851</v>
+        <v>0.1542</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2263</v>
+        <v>-0.1909</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5462</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3696</v>
+        <v>1.3468</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1766</v>
+        <v>-0.3564</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3696</v>
+        <v>1.3468</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3727</v>
+        <v>1.4022</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1766</v>
+        <v>-0.3564</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5493</v>
+        <v>1.0458</v>
       </c>
       <c r="N25" t="n">
         <v>190</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>glow</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4987</v>
+        <v>0.8879</v>
       </c>
       <c r="C26" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1383</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2452</v>
+        <v>-0.2372</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4987</v>
+        <v>0.8879</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0304</v>
+        <v>0.8879</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5317</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0304</v>
+        <v>0.8879</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0304</v>
+        <v>0.8879</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5317</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L26" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4987</v>
+        <v>0.8879</v>
       </c>
       <c r="N26" t="n">
-        <v>203</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0255</v>
+        <v>0.0954</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3787</v>
+        <v>-0.3616</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1636</v>
+        <v>0.6123</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.111</v>
+        <v>0.3562</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0173</v>
+        <v>0.0555</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4881</v>
+        <v>-0.4772</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.111</v>
+        <v>0.3562</v>
       </c>
       <c r="F28" t="n">
-        <v>0.64</v>
+        <v>0.7597</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.751</v>
+        <v>-0.4035</v>
       </c>
       <c r="H28" t="n">
-        <v>0.64</v>
+        <v>0.7597</v>
       </c>
       <c r="I28" t="n">
-        <v>0.64</v>
+        <v>0.7597</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.751</v>
+        <v>-0.4035</v>
       </c>
       <c r="K28" t="n">
         <v>116</v>
@@ -1725,7 +1725,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.111</v>
+        <v>0.3562</v>
       </c>
       <c r="N28" t="n">
         <v>254</v>
@@ -1734,231 +1734,231 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>solo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.047</v>
+        <v>0.0092</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5642</v>
+        <v>-0.6112</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.302</v>
+        <v>0.0593</v>
       </c>
       <c r="N29" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>solo</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0549</v>
+        <v>-0.0019</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5843</v>
+        <v>-0.6435</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3525</v>
+        <v>-0.0121</v>
       </c>
       <c r="N30" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0801</v>
+        <v>-0.012</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6489</v>
+        <v>-0.6727</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5373</v>
+        <v>-0.336</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0837</v>
+        <v>-0.0523</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.658</v>
+        <v>-0.7897</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5373</v>
+        <v>-0.336</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7117</v>
+        <v>-0.336</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1744</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7117</v>
+        <v>-0.336</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7177</v>
+        <v>-0.336</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1744</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="L32" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5433</v>
+        <v>-0.336</v>
       </c>
       <c r="N32" t="n">
-        <v>274</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6311</v>
+        <v>-0.3819</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0983</v>
+        <v>-0.0595</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6953</v>
+        <v>-0.8104</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6311</v>
+        <v>-0.3819</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6311</v>
+        <v>-0.4806</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0987</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6311</v>
+        <v>-0.4806</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6311</v>
+        <v>-0.5004</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.0987</v>
       </c>
       <c r="K33" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6311</v>
+        <v>-0.4016999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1047</v>
+        <v>-0.0595</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7118</v>
+        <v>-0.8105</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6724</v>
+        <v>-0.3821</v>
       </c>
       <c r="N34" t="n">
         <v>125</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.138</v>
+        <v>-0.0794</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8681</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8861</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>91</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.976</v>
+        <v>-0.5926</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.152</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8327</v>
+        <v>-0.9055</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.976</v>
+        <v>-0.5926</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1607</v>
+        <v>-1.2895</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1847</v>
+        <v>0.6969</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1607</v>
+        <v>-1.2895</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9408</v>
+        <v>-0.6705</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1847</v>
+        <v>0.6969</v>
       </c>
       <c r="K36" t="n">
         <v>139</v>
@@ -2093,7 +2093,7 @@
         <v>117</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7561</v>
+        <v>0.02639999999999998</v>
       </c>
       <c r="N36" t="n">
         <v>256</v>
@@ -2102,81 +2102,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.37</v>
+        <v>-0.6864</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2133</v>
+        <v>-0.1069</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9897</v>
+        <v>-0.9479</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.37</v>
+        <v>-0.6864</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.37</v>
+        <v>-0.4394</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.247</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.37</v>
+        <v>-0.4394</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.37</v>
+        <v>-0.4394</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.247</v>
       </c>
       <c r="K37" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.37</v>
+        <v>-0.6864</v>
       </c>
       <c r="N37" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4145</v>
+        <v>-0.9387</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2203</v>
+        <v>-0.1462</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0074</v>
+        <v>-1.0618</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4145</v>
+        <v>-0.9387</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8477</v>
+        <v>-1.2911</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5668</v>
+        <v>0.3524</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8477</v>
+        <v>-1.2911</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8477</v>
+        <v>-1.2911</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5668</v>
+        <v>0.3524</v>
       </c>
       <c r="K38" t="n">
         <v>116</v>
@@ -2185,7 +2185,7 @@
         <v>138</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4145</v>
+        <v>-0.9386999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>254</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4408</v>
+        <v>-0.9794</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2244</v>
+        <v>-0.1525</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0179</v>
+        <v>-1.0802</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4408</v>
+        <v>-0.9794</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5856</v>
+        <v>-0.9794</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1448</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5856</v>
+        <v>-0.9794</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5856</v>
+        <v>-0.9794</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1448</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4408</v>
+        <v>-0.9794</v>
       </c>
       <c r="N39" t="n">
-        <v>254</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3114</v>
+        <v>-0.2651</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2407</v>
+        <v>-1.4065</v>
       </c>
       <c r="E40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2</v>
+        <v>-1.7023</v>
       </c>
       <c r="N40" t="n">
         <v>91</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0346</v>
+        <v>-2.3562</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4726</v>
+        <v>-0.3669</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6529</v>
+        <v>-1.7017</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0346</v>
+        <v>-2.3562</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3552</v>
+        <v>-1.2246</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6794</v>
+        <v>-1.1316</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3552</v>
+        <v>-1.2246</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3666</v>
+        <v>-1.275</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6794</v>
+        <v>-1.1316</v>
       </c>
       <c r="K41" t="n">
         <v>145</v>
@@ -2323,7 +2323,7 @@
         <v>129</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.046</v>
+        <v>-2.4066</v>
       </c>
       <c r="N41" t="n">
         <v>274</v>
@@ -2429,10 +2429,10 @@
         <v>1.87</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0082</v>
+        <v>0.9355</v>
       </c>
       <c r="J2" t="n">
-        <v>19.1558</v>
+        <v>17.7745</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7432</v>
+        <v>0.6966</v>
       </c>
       <c r="J3" t="n">
-        <v>14.1208</v>
+        <v>13.2354</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5858</v>
+        <v>0.58</v>
       </c>
       <c r="J4" t="n">
-        <v>11.1302</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.49</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5735</v>
+        <v>0.5699</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8965</v>
+        <v>10.8281</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3053</v>
+        <v>0.3305</v>
       </c>
       <c r="J6" t="n">
-        <v>5.8007</v>
+        <v>6.2795</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4212</v>
+        <v>0.3812</v>
       </c>
       <c r="J7" t="n">
-        <v>8.002800000000001</v>
+        <v>7.2428</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1378</v>
+        <v>-0.1356</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.6182</v>
+        <v>-2.5764</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.48</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7169</v>
+        <v>-0.4891</v>
       </c>
       <c r="J9" t="n">
-        <v>-13.6211</v>
+        <v>-9.292899999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.38</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.5839</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.0987</v>
+        <v>-11.0941</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.32</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9215</v>
+        <v>-0.6411</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.5085</v>
+        <v>-12.1809</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2253</v>
+        <v>0.2161</v>
       </c>
       <c r="J12" t="n">
-        <v>4.506</v>
+        <v>4.322</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.93</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0378</v>
+        <v>-0.0606</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.756</v>
+        <v>-1.212</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3885</v>
+        <v>-0.274</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.77</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6299</v>
+        <v>-0.4231</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.598</v>
+        <v>-8.462</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.5718</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.644</v>
+        <v>-11.436</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7678</v>
+        <v>1.5122</v>
       </c>
       <c r="J17" t="n">
-        <v>35.356</v>
+        <v>30.244</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4073</v>
+        <v>1.283</v>
       </c>
       <c r="J18" t="n">
-        <v>28.146</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6877</v>
+        <v>0.8091</v>
       </c>
       <c r="J19" t="n">
-        <v>13.754</v>
+        <v>16.182</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5321</v>
+        <v>0.6494</v>
       </c>
       <c r="J20" t="n">
-        <v>10.642</v>
+        <v>12.988</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5095</v>
+        <v>0.6258</v>
       </c>
       <c r="J21" t="n">
-        <v>10.19</v>
+        <v>12.516</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="J22" t="n">
-        <v>12.8084</v>
+        <v>15.378</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1756</v>
+        <v>-0.1242</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.8632</v>
+        <v>-2.7324</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.88</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2208</v>
+        <v>-0.145</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.8576</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.72</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4713</v>
+        <v>-0.3048</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.3686</v>
+        <v>-6.7056</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.539</v>
+        <v>-0.3524</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.858</v>
+        <v>-7.7528</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8062</v>
+        <v>1.531</v>
       </c>
       <c r="J27" t="n">
-        <v>39.7364</v>
+        <v>33.682</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7776</v>
+        <v>0.7872</v>
       </c>
       <c r="J28" t="n">
-        <v>17.1072</v>
+        <v>17.3184</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3639</v>
+        <v>0.432</v>
       </c>
       <c r="J29" t="n">
-        <v>8.005800000000001</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3675</v>
+        <v>-0.2886</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.085000000000001</v>
+        <v>-6.3492</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4553</v>
+        <v>-0.3802</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.0166</v>
+        <v>-8.3644</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0265</v>
+        <v>0.7388</v>
       </c>
       <c r="J32" t="n">
-        <v>29.7685</v>
+        <v>21.4252</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6082</v>
+        <v>0.4889</v>
       </c>
       <c r="J33" t="n">
-        <v>17.6378</v>
+        <v>14.1781</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4403</v>
+        <v>0.4008</v>
       </c>
       <c r="J34" t="n">
-        <v>12.7687</v>
+        <v>11.6232</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1459</v>
+        <v>0.1992</v>
       </c>
       <c r="J35" t="n">
-        <v>4.2311</v>
+        <v>5.7768</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5112</v>
+        <v>-0.4446</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.8248</v>
+        <v>-12.8934</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2508</v>
+        <v>0.2634</v>
       </c>
       <c r="J37" t="n">
-        <v>7.2732</v>
+        <v>7.6386</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0963</v>
+        <v>0.0785</v>
       </c>
       <c r="J38" t="n">
-        <v>2.7927</v>
+        <v>2.2765</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0708</v>
+        <v>0.0493</v>
       </c>
       <c r="J39" t="n">
-        <v>2.0532</v>
+        <v>1.4297</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2234</v>
+        <v>-0.1386</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.4786</v>
+        <v>-4.0194</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.3482</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.5092</v>
+        <v>-10.0978</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9681</v>
+        <v>0.7012</v>
       </c>
       <c r="J42" t="n">
-        <v>26.1387</v>
+        <v>18.9324</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8793</v>
+        <v>0.6464</v>
       </c>
       <c r="J43" t="n">
-        <v>23.7411</v>
+        <v>17.4528</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1856</v>
+        <v>0.2326</v>
       </c>
       <c r="J44" t="n">
-        <v>5.0112</v>
+        <v>6.2802</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2326</v>
+        <v>-0.1628</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.2802</v>
+        <v>-4.3956</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4236</v>
+        <v>-0.355</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.4372</v>
+        <v>-9.585000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6063</v>
+        <v>0.5687</v>
       </c>
       <c r="J47" t="n">
-        <v>16.3701</v>
+        <v>15.3549</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1162</v>
+        <v>-0.0827</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.1374</v>
+        <v>-2.2329</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2035</v>
+        <v>-0.1274</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.4945</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4392</v>
+        <v>-0.2806</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.8584</v>
+        <v>-7.5762</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4531</v>
+        <v>-0.2903</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.2337</v>
+        <v>-7.8381</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7755</v>
+        <v>1.2664</v>
       </c>
       <c r="J52" t="n">
-        <v>51.4895</v>
+        <v>36.7256</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1.384</v>
+        <v>0.9764</v>
       </c>
       <c r="J53" t="n">
-        <v>40.136</v>
+        <v>28.3156</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1485</v>
+        <v>0.2281</v>
       </c>
       <c r="J54" t="n">
-        <v>4.3065</v>
+        <v>6.6149</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4107</v>
+        <v>-0.3309</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.9103</v>
+        <v>-9.5961</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4954</v>
+        <v>-0.4203</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.3666</v>
+        <v>-12.1887</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2406</v>
+        <v>0.2482</v>
       </c>
       <c r="J57" t="n">
-        <v>6.9774</v>
+        <v>7.1978</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2232</v>
+        <v>0.2267</v>
       </c>
       <c r="J58" t="n">
-        <v>6.4728</v>
+        <v>6.5743</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0435</v>
+        <v>0.0148</v>
       </c>
       <c r="J59" t="n">
-        <v>1.2615</v>
+        <v>0.4292</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3007</v>
+        <v>-0.1891</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.7203</v>
+        <v>-5.4839</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6335</v>
+        <v>-0.4206</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.3715</v>
+        <v>-12.1974</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.55</v>
       </c>
       <c r="I62" t="n">
-        <v>1.277</v>
+        <v>0.9099</v>
       </c>
       <c r="J62" t="n">
-        <v>30.648</v>
+        <v>21.8376</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.45</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0745</v>
+        <v>0.785</v>
       </c>
       <c r="J63" t="n">
-        <v>25.788</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9003</v>
+        <v>0.6832</v>
       </c>
       <c r="J64" t="n">
-        <v>21.6072</v>
+        <v>16.3968</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2793</v>
+        <v>0.3514</v>
       </c>
       <c r="J65" t="n">
-        <v>6.7032</v>
+        <v>8.4336</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.96</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3234</v>
+        <v>-0.2393</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.7616</v>
+        <v>-5.7432</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1645</v>
+        <v>0.1391</v>
       </c>
       <c r="J67" t="n">
-        <v>3.948</v>
+        <v>3.3384</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.11</v>
+        <v>-0.1066</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.64</v>
+        <v>-2.5584</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.49</v>
+        <v>-0.326</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.76</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5187</v>
+        <v>-0.3449</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.4488</v>
+        <v>-8.2776</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5743</v>
+        <v>-0.3825</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.7832</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9107</v>
+        <v>0.6734</v>
       </c>
       <c r="J72" t="n">
-        <v>22.7675</v>
+        <v>16.835</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.29</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7729</v>
+        <v>0.5924</v>
       </c>
       <c r="J73" t="n">
-        <v>19.3225</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.2</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5391</v>
+        <v>0.4678</v>
       </c>
       <c r="J74" t="n">
-        <v>13.4775</v>
+        <v>11.695</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2979</v>
+        <v>0.3488</v>
       </c>
       <c r="J75" t="n">
-        <v>7.4475</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1203</v>
+        <v>-0.0466</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.0075</v>
+        <v>-1.165</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.5</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7914</v>
+        <v>0.7244</v>
       </c>
       <c r="J77" t="n">
-        <v>19.785</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1963</v>
+        <v>-0.126</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.9075</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3477</v>
+        <v>-0.2196</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.692500000000001</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3477</v>
+        <v>-0.2196</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.692500000000001</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.59</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6459</v>
+        <v>-0.4298</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.1475</v>
+        <v>-10.745</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>0.968</v>
+        <v>0.6994</v>
       </c>
       <c r="J82" t="n">
-        <v>27.104</v>
+        <v>19.5832</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6186</v>
+        <v>0.4763</v>
       </c>
       <c r="J83" t="n">
-        <v>17.3208</v>
+        <v>13.3364</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.87</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2896</v>
+        <v>-0.172</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.1088</v>
+        <v>-4.816</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.388</v>
       </c>
       <c r="J85" t="n">
-        <v>-16.5536</v>
+        <v>-10.864</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.628</v>
+        <v>-0.4156</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.584</v>
+        <v>-11.6368</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4627</v>
+        <v>0.3713</v>
       </c>
       <c r="J87" t="n">
-        <v>12.9556</v>
+        <v>10.3964</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.32</v>
+        <v>0.2756</v>
       </c>
       <c r="J88" t="n">
-        <v>8.960000000000001</v>
+        <v>7.7168</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3043</v>
+        <v>0.2631</v>
       </c>
       <c r="J89" t="n">
-        <v>8.5204</v>
+        <v>7.3668</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2542</v>
+        <v>0.2251</v>
       </c>
       <c r="J90" t="n">
-        <v>7.1176</v>
+        <v>6.3028</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3088</v>
+        <v>-0.1816</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.6464</v>
+        <v>-5.0848</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.68</v>
       </c>
       <c r="I92" t="n">
-        <v>1.564</v>
+        <v>1.0923</v>
       </c>
       <c r="J92" t="n">
-        <v>45.356</v>
+        <v>31.6767</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.858</v>
+        <v>0.6441</v>
       </c>
       <c r="J93" t="n">
-        <v>24.882</v>
+        <v>18.6789</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.262</v>
+        <v>0.3266</v>
       </c>
       <c r="J94" t="n">
-        <v>7.598</v>
+        <v>9.471399999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.96</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2977</v>
+        <v>-0.2185</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.6333</v>
+        <v>-6.3365</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3305</v>
+        <v>-0.252</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.5845</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4126</v>
+        <v>0.4123</v>
       </c>
       <c r="J97" t="n">
-        <v>11.9654</v>
+        <v>11.9567</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1844</v>
+        <v>0.1728</v>
       </c>
       <c r="J98" t="n">
-        <v>5.3476</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3944</v>
+        <v>-0.254</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.4376</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4382</v>
+        <v>-0.2831</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.7078</v>
+        <v>-8.209899999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5613</v>
+        <v>-0.3689</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.2777</v>
+        <v>-10.6981</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3993</v>
+        <v>0.4073</v>
       </c>
       <c r="J102" t="n">
-        <v>11.979</v>
+        <v>12.219</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0049</v>
+        <v>0.0003</v>
       </c>
       <c r="J103" t="n">
-        <v>0.147</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1127</v>
+        <v>-0.0629</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.381</v>
+        <v>-1.887</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.91</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2092</v>
+        <v>-0.1226</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.276</v>
+        <v>-3.678</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2266</v>
+        <v>-0.1338</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.798</v>
+        <v>-4.014</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1563</v>
+        <v>0.8208</v>
       </c>
       <c r="J107" t="n">
-        <v>34.689</v>
+        <v>24.624</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8316</v>
+        <v>0.6178</v>
       </c>
       <c r="J108" t="n">
-        <v>24.948</v>
+        <v>18.534</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3798</v>
+        <v>0.3717</v>
       </c>
       <c r="J109" t="n">
-        <v>11.394</v>
+        <v>11.151</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3351</v>
+        <v>-0.2645</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.053</v>
+        <v>-7.935</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.638</v>
+        <v>-0.579</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.14</v>
+        <v>-17.37</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.96</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1119</v>
+        <v>0.7468</v>
       </c>
       <c r="J112" t="n">
-        <v>23.3499</v>
+        <v>15.6828</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.69</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.5927</v>
       </c>
       <c r="J113" t="n">
-        <v>17.6232</v>
+        <v>12.4467</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.65</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7958</v>
+        <v>0.5694</v>
       </c>
       <c r="J114" t="n">
-        <v>16.7118</v>
+        <v>11.9574</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1207</v>
       </c>
       <c r="J115" t="n">
-        <v>1.7241</v>
+        <v>2.5347</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1144</v>
+        <v>-0.0427</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.4024</v>
+        <v>-0.8967000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3597</v>
+        <v>0.3066</v>
       </c>
       <c r="J117" t="n">
-        <v>7.5537</v>
+        <v>6.4386</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0667</v>
+        <v>0.0162</v>
       </c>
       <c r="J118" t="n">
-        <v>1.4007</v>
+        <v>0.3402</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.6259</v>
+        <v>-0.4236</v>
       </c>
       <c r="J119" t="n">
-        <v>-13.1439</v>
+        <v>-8.8956</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.7589</v>
+        <v>-0.5173</v>
       </c>
       <c r="J120" t="n">
-        <v>-15.9369</v>
+        <v>-10.8633</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9306</v>
+        <v>-0.6484</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.5426</v>
+        <v>-13.6164</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3037</v>
+        <v>0.3306</v>
       </c>
       <c r="J122" t="n">
-        <v>7.5925</v>
+        <v>8.265000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2386</v>
+        <v>0.2538</v>
       </c>
       <c r="J123" t="n">
-        <v>5.965</v>
+        <v>6.345</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0746</v>
+        <v>-0.0479</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.865</v>
+        <v>-1.1975</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1632</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.08</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4884</v>
+        <v>-0.314</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.21</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2946</v>
+        <v>0.9151</v>
       </c>
       <c r="J127" t="n">
-        <v>32.365</v>
+        <v>22.8775</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8535</v>
+        <v>0.6427</v>
       </c>
       <c r="J128" t="n">
-        <v>21.3375</v>
+        <v>16.0675</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.3</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7836</v>
+        <v>0.6025</v>
       </c>
       <c r="J129" t="n">
-        <v>19.59</v>
+        <v>15.0625</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3003</v>
+        <v>-0.2205</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.5075</v>
+        <v>-5.5125</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3644</v>
+        <v>-0.2862</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.109999999999999</v>
+        <v>-7.155</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.38</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5899</v>
+        <v>0.7174</v>
       </c>
       <c r="J132" t="n">
-        <v>17.697</v>
+        <v>21.522</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3038</v>
+        <v>0.3585</v>
       </c>
       <c r="J133" t="n">
-        <v>9.114000000000001</v>
+        <v>10.755</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.272</v>
+        <v>0.322</v>
       </c>
       <c r="J134" t="n">
-        <v>8.16</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1264</v>
+        <v>-0.0598</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.792</v>
+        <v>-1.794</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3752</v>
+        <v>-0.2297</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.256</v>
+        <v>-6.891</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.17</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5796</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>17.388</v>
+        <v>16.044</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3537</v>
+        <v>0.3139</v>
       </c>
       <c r="J138" t="n">
-        <v>10.611</v>
+        <v>9.417</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2562</v>
+        <v>0.2239</v>
       </c>
       <c r="J139" t="n">
-        <v>7.686</v>
+        <v>6.717</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4061</v>
+        <v>-0.354</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.183</v>
+        <v>-10.62</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4915</v>
+        <v>-0.4389</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.745</v>
+        <v>-13.167</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.18</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3424</v>
+        <v>0.3918</v>
       </c>
       <c r="J142" t="n">
-        <v>10.272</v>
+        <v>11.754</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3424</v>
+        <v>0.3918</v>
       </c>
       <c r="J143" t="n">
-        <v>10.272</v>
+        <v>11.754</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1479</v>
+        <v>-0.0794</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.437</v>
+        <v>-2.382</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1479</v>
+        <v>-0.0794</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.437</v>
+        <v>-2.382</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.221</v>
+        <v>-0.1268</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.63</v>
+        <v>-3.804</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5949</v>
+        <v>1.3873</v>
       </c>
       <c r="J147" t="n">
-        <v>47.847</v>
+        <v>41.619</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1547</v>
+        <v>0.1823</v>
       </c>
       <c r="J148" t="n">
-        <v>4.641</v>
+        <v>5.469</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0395</v>
+        <v>0.079</v>
       </c>
       <c r="J149" t="n">
-        <v>1.185</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6197</v>
+        <v>-0.5638</v>
       </c>
       <c r="J150" t="n">
-        <v>-18.591</v>
+        <v>-16.914</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6698</v>
+        <v>-0.6166</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.094</v>
+        <v>-18.498</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3565</v>
+        <v>0.4096</v>
       </c>
       <c r="J152" t="n">
-        <v>10.695</v>
+        <v>12.288</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1584</v>
+        <v>0.1765</v>
       </c>
       <c r="J153" t="n">
-        <v>4.752</v>
+        <v>5.295</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1172</v>
+        <v>0.1331</v>
       </c>
       <c r="J154" t="n">
-        <v>3.516</v>
+        <v>3.993</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0584</v>
+        <v>-0.0236</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.752</v>
+        <v>-0.708</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2713</v>
+        <v>-0.1602</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.138999999999999</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9991</v>
+        <v>0.9726</v>
       </c>
       <c r="J157" t="n">
-        <v>29.973</v>
+        <v>29.178</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3451</v>
+        <v>0.3103</v>
       </c>
       <c r="J158" t="n">
-        <v>10.353</v>
+        <v>9.308999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2549</v>
+        <v>-0.2052</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.647</v>
+        <v>-6.156</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4693</v>
+        <v>-0.4145</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.079</v>
+        <v>-12.435</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4693</v>
+        <v>-0.4145</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.079</v>
+        <v>-12.435</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.6864</v>
       </c>
       <c r="J162" t="n">
-        <v>14.9006</v>
+        <v>17.8464</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2141</v>
+        <v>-0.1442</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.5666</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.83</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3037</v>
+        <v>-0.1953</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.8962</v>
+        <v>-5.0778</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.72</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4687</v>
+        <v>-0.3035</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.1862</v>
+        <v>-7.891</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.9038</v>
+        <v>-8.387600000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4026</v>
+        <v>1.2651</v>
       </c>
       <c r="J167" t="n">
-        <v>36.4676</v>
+        <v>32.8926</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.49</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1474</v>
+        <v>1.1054</v>
       </c>
       <c r="J168" t="n">
-        <v>29.8324</v>
+        <v>28.7404</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4257</v>
+        <v>0.5143</v>
       </c>
       <c r="J169" t="n">
-        <v>11.0682</v>
+        <v>13.3718</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.17</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3753</v>
+        <v>0.4639</v>
       </c>
       <c r="J170" t="n">
-        <v>9.7578</v>
+        <v>12.0614</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.09</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1625</v>
+        <v>0.2476</v>
       </c>
       <c r="J171" t="n">
-        <v>4.225</v>
+        <v>6.4376</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2225</v>
+        <v>0.22</v>
       </c>
       <c r="J172" t="n">
-        <v>5.785</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0969</v>
+        <v>0.0669</v>
       </c>
       <c r="J173" t="n">
-        <v>2.5194</v>
+        <v>1.7394</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1027</v>
+        <v>-0.0885</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.6702</v>
+        <v>-2.301</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.045400000000001</v>
+        <v>-5.8266</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.58</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6504</v>
+        <v>-0.4338</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.9104</v>
+        <v>-11.2788</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0915</v>
+        <v>1.0649</v>
       </c>
       <c r="J177" t="n">
-        <v>28.379</v>
+        <v>27.6874</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8689</v>
       </c>
       <c r="J178" t="n">
-        <v>22.1338</v>
+        <v>22.5914</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.28</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7047</v>
+        <v>0.7347</v>
       </c>
       <c r="J179" t="n">
-        <v>18.3222</v>
+        <v>19.1022</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5041</v>
+        <v>0.5745</v>
       </c>
       <c r="J180" t="n">
-        <v>13.1066</v>
+        <v>14.937</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.01</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0851</v>
+        <v>-0.008</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.2126</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.95</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1351</v>
+        <v>1.0304</v>
       </c>
       <c r="J182" t="n">
-        <v>27.2424</v>
+        <v>24.7296</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.8</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9871</v>
+        <v>0.9062</v>
       </c>
       <c r="J183" t="n">
-        <v>23.6904</v>
+        <v>21.7488</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1501</v>
+        <v>0.1772</v>
       </c>
       <c r="J184" t="n">
-        <v>3.6024</v>
+        <v>4.2528</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1933</v>
+        <v>-0.0964</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.6392</v>
+        <v>-2.3136</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3395</v>
+        <v>-0.2004</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.148</v>
+        <v>-4.8096</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4667</v>
+        <v>0.4144</v>
       </c>
       <c r="J187" t="n">
-        <v>11.2008</v>
+        <v>9.945600000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0189</v>
       </c>
       <c r="J188" t="n">
-        <v>1.6344</v>
+        <v>0.4536</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.3552</v>
       </c>
       <c r="J189" t="n">
-        <v>-12.8352</v>
+        <v>-8.524800000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.58</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6293</v>
+        <v>-0.4208</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.1032</v>
+        <v>-10.0992</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.49</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5042</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.8416</v>
+        <v>-12.1008</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5515</v>
+        <v>0.6583</v>
       </c>
       <c r="J192" t="n">
-        <v>19.3025</v>
+        <v>23.0405</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3601</v>
+        <v>0.4067</v>
       </c>
       <c r="J193" t="n">
-        <v>12.6035</v>
+        <v>14.2345</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3301</v>
+        <v>0.3689</v>
       </c>
       <c r="J194" t="n">
-        <v>11.5535</v>
+        <v>12.9115</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4909</v>
+        <v>-0.3154</v>
       </c>
       <c r="J195" t="n">
-        <v>-17.1815</v>
+        <v>-11.039</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7153</v>
+        <v>-0.482</v>
       </c>
       <c r="J196" t="n">
-        <v>-25.0355</v>
+        <v>-16.87</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>1.017</v>
+        <v>1.0007</v>
       </c>
       <c r="J197" t="n">
-        <v>35.595</v>
+        <v>35.0245</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4523</v>
+        <v>0.4696</v>
       </c>
       <c r="J198" t="n">
-        <v>15.8305</v>
+        <v>16.436</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4523</v>
+        <v>0.4696</v>
       </c>
       <c r="J199" t="n">
-        <v>15.8305</v>
+        <v>16.436</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.07</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1682</v>
+        <v>0.2255</v>
       </c>
       <c r="J200" t="n">
-        <v>5.887</v>
+        <v>7.8925</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1059</v>
+        <v>-0.0374</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.7065</v>
+        <v>-1.309</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.324</v>
+        <v>1.229</v>
       </c>
       <c r="J202" t="n">
-        <v>29.128</v>
+        <v>27.038</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.61</v>
       </c>
       <c r="I203" t="n">
-        <v>1.324</v>
+        <v>1.229</v>
       </c>
       <c r="J203" t="n">
-        <v>29.128</v>
+        <v>27.038</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.879</v>
+        <v>0.9787</v>
       </c>
       <c r="J204" t="n">
-        <v>19.338</v>
+        <v>21.5314</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8106</v>
+        <v>0.9223</v>
       </c>
       <c r="J205" t="n">
-        <v>17.8332</v>
+        <v>20.2906</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.21</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4259</v>
+        <v>0.5354</v>
       </c>
       <c r="J206" t="n">
-        <v>9.3698</v>
+        <v>11.7788</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2364</v>
+        <v>0.2315</v>
       </c>
       <c r="J207" t="n">
-        <v>5.2008</v>
+        <v>5.093</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.77</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2944</v>
+        <v>-0.2332</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.4768</v>
+        <v>-5.1304</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.7</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4257</v>
+        <v>-0.2985</v>
       </c>
       <c r="J209" t="n">
-        <v>-9.365399999999999</v>
+        <v>-6.567</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.58</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6087</v>
+        <v>-0.4099</v>
       </c>
       <c r="J210" t="n">
-        <v>-13.3914</v>
+        <v>-9.017799999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7534</v>
+        <v>-0.5127</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.5748</v>
+        <v>-11.2794</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.91</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0767</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.6874</v>
+        <v>-1.914</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.179</v>
+        <v>-0.1557</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.938</v>
+        <v>-3.4254</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.7</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4447</v>
+        <v>-0.3023</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.7834</v>
+        <v>-6.6506</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.63</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5493</v>
+        <v>-0.3679</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.0846</v>
+        <v>-8.0938</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5634</v>
+        <v>-0.3772</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.3948</v>
+        <v>-8.298400000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.64</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8017</v>
+        <v>0.7327</v>
       </c>
       <c r="J217" t="n">
-        <v>17.6374</v>
+        <v>16.1194</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.58</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7352</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>16.1744</v>
+        <v>14.7818</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.49</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6297</v>
+        <v>0.5799</v>
       </c>
       <c r="J219" t="n">
-        <v>13.8534</v>
+        <v>12.7578</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.21</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2504</v>
+        <v>0.2724</v>
       </c>
       <c r="J220" t="n">
-        <v>5.5088</v>
+        <v>5.9928</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1664</v>
+        <v>0.196</v>
       </c>
       <c r="J221" t="n">
-        <v>3.6608</v>
+        <v>4.312</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2736</v>
+        <v>1.2021</v>
       </c>
       <c r="J222" t="n">
-        <v>26.7456</v>
+        <v>25.2441</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0124</v>
+        <v>1.0613</v>
       </c>
       <c r="J223" t="n">
-        <v>21.2604</v>
+        <v>22.2873</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.46</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9817</v>
+        <v>1.0493</v>
       </c>
       <c r="J224" t="n">
-        <v>20.6157</v>
+        <v>22.0353</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9333</v>
+        <v>1.0229</v>
       </c>
       <c r="J225" t="n">
-        <v>19.5993</v>
+        <v>21.4809</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.38</v>
       </c>
       <c r="I226" t="n">
-        <v>0.799</v>
+        <v>0.9182</v>
       </c>
       <c r="J226" t="n">
-        <v>16.779</v>
+        <v>19.2822</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.86</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1053</v>
+        <v>-0.1122</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.2113</v>
+        <v>-2.3562</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.73</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3108</v>
+        <v>-0.2555</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.5268</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4584</v>
+        <v>-0.3425</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.6264</v>
+        <v>-7.1925</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.51</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6756</v>
+        <v>-0.4608</v>
       </c>
       <c r="J230" t="n">
-        <v>-14.1876</v>
+        <v>-9.6768</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.4</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8219</v>
+        <v>-0.5649</v>
       </c>
       <c r="J231" t="n">
-        <v>-17.2599</v>
+        <v>-11.8629</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1777</v>
+        <v>1.1107</v>
       </c>
       <c r="J232" t="n">
-        <v>30.6202</v>
+        <v>28.8782</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.42</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0744</v>
+        <v>1.0443</v>
       </c>
       <c r="J233" t="n">
-        <v>27.9344</v>
+        <v>27.1518</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5324</v>
+        <v>0.5411</v>
       </c>
       <c r="J234" t="n">
-        <v>13.8424</v>
+        <v>14.0686</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4382</v>
+        <v>-0.3661</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.3932</v>
+        <v>-9.518599999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5989</v>
+        <v>-0.5352</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.5714</v>
+        <v>-13.9152</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3625</v>
+        <v>0.4045</v>
       </c>
       <c r="J237" t="n">
-        <v>9.425000000000001</v>
+        <v>10.517</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.13</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3012</v>
+        <v>0.326</v>
       </c>
       <c r="J238" t="n">
-        <v>7.8312</v>
+        <v>8.476000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2732</v>
+        <v>-0.1701</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.1032</v>
+        <v>-4.4226</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3213</v>
+        <v>-0.201</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.3538</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5208</v>
+        <v>-0.3382</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.5408</v>
+        <v>-8.793200000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2798</v>
+        <v>1.1787</v>
       </c>
       <c r="J242" t="n">
-        <v>34.5546</v>
+        <v>31.8249</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.9042</v>
+        <v>0.9061</v>
       </c>
       <c r="J243" t="n">
-        <v>24.4134</v>
+        <v>24.4647</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3196</v>
+        <v>0.3838</v>
       </c>
       <c r="J244" t="n">
-        <v>8.629200000000001</v>
+        <v>10.3626</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0133</v>
+        <v>0.0835</v>
       </c>
       <c r="J245" t="n">
-        <v>0.3591</v>
+        <v>2.2545</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.98</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.225</v>
+        <v>-0.1457</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.075</v>
+        <v>-3.9339</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2429</v>
+        <v>0.2503</v>
       </c>
       <c r="J247" t="n">
-        <v>6.5583</v>
+        <v>6.7581</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2429</v>
+        <v>0.2503</v>
       </c>
       <c r="J248" t="n">
-        <v>6.5583</v>
+        <v>6.7581</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1236</v>
+        <v>-0.0927</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.3372</v>
+        <v>-2.5029</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3457</v>
+        <v>-0.2189</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.3339</v>
+        <v>-5.9103</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.556</v>
+        <v>-0.3641</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.012</v>
+        <v>-9.8307</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.96</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0031</v>
+        <v>-0.0306</v>
       </c>
       <c r="J252" t="n">
-        <v>0.0682</v>
+        <v>-0.6732</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.88</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1438</v>
+        <v>-0.129</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.1636</v>
+        <v>-2.838</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3799</v>
+        <v>-0.2597</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.357799999999999</v>
+        <v>-5.7134</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3799</v>
+        <v>-0.2597</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.357799999999999</v>
+        <v>-5.7134</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6917</v>
+        <v>-0.4661</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.2174</v>
+        <v>-10.2542</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.52</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6916</v>
+        <v>0.623</v>
       </c>
       <c r="J257" t="n">
-        <v>15.2152</v>
+        <v>13.706</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.47</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6329</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>13.9238</v>
+        <v>12.5422</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.44</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5965</v>
+        <v>0.5381</v>
       </c>
       <c r="J259" t="n">
-        <v>13.123</v>
+        <v>11.8382</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1691</v>
+        <v>0.1929</v>
       </c>
       <c r="J260" t="n">
-        <v>3.7202</v>
+        <v>4.2438</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0045</v>
+        <v>0.0453</v>
       </c>
       <c r="J261" t="n">
-        <v>0.099</v>
+        <v>0.9966</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.84</v>
       </c>
       <c r="I262" t="n">
-        <v>1.8265</v>
+        <v>1.5452</v>
       </c>
       <c r="J262" t="n">
-        <v>52.9685</v>
+        <v>44.8108</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6813</v>
+        <v>0.7129</v>
       </c>
       <c r="J263" t="n">
-        <v>19.7577</v>
+        <v>20.6741</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.26</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6905</v>
       </c>
       <c r="J264" t="n">
-        <v>18.9283</v>
+        <v>20.0245</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.1</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2121</v>
+        <v>0.2898</v>
       </c>
       <c r="J265" t="n">
-        <v>6.1509</v>
+        <v>8.404199999999999</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7423</v>
+        <v>-0.6875</v>
       </c>
       <c r="J266" t="n">
-        <v>-21.5267</v>
+        <v>-19.9375</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.47</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>22.2024</v>
+        <v>27.7588</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1535</v>
+        <v>-0.1135</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.4515</v>
+        <v>-3.2915</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2573</v>
+        <v>-0.1658</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.4617</v>
+        <v>-4.8082</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4988</v>
+        <v>-0.3239</v>
       </c>
       <c r="J270" t="n">
-        <v>-14.4652</v>
+        <v>-9.3931</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6909</v>
+        <v>-0.4637</v>
       </c>
       <c r="J271" t="n">
-        <v>-20.0361</v>
+        <v>-13.4473</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.06</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8006</v>
       </c>
       <c r="J272" t="n">
-        <v>51.4825</v>
+        <v>45.015</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.35</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8709</v>
+        <v>0.8895</v>
       </c>
       <c r="J273" t="n">
-        <v>21.7725</v>
+        <v>22.2375</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.12</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2636</v>
+        <v>0.3431</v>
       </c>
       <c r="J274" t="n">
-        <v>6.59</v>
+        <v>8.577500000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.02</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0455</v>
+        <v>0.0317</v>
       </c>
       <c r="J275" t="n">
-        <v>-1.1375</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.77</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8136</v>
+        <v>-0.766</v>
       </c>
       <c r="J276" t="n">
-        <v>-20.34</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3382</v>
+        <v>0.3716</v>
       </c>
       <c r="J277" t="n">
-        <v>8.455</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.08</v>
       </c>
       <c r="I278" t="n">
-        <v>0.224</v>
+        <v>0.2273</v>
       </c>
       <c r="J278" t="n">
-        <v>5.6</v>
+        <v>5.6825</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2323</v>
+        <v>-0.1472</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.8075</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.675</v>
+        <v>-4.205</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5954</v>
+        <v>-0.3926</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.885</v>
+        <v>-9.815</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.91</v>
       </c>
       <c r="I282" t="n">
-        <v>1.837</v>
+        <v>1.5604</v>
       </c>
       <c r="J282" t="n">
-        <v>34.903</v>
+        <v>29.6476</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.69</v>
       </c>
       <c r="I283" t="n">
-        <v>1.4463</v>
+        <v>1.3117</v>
       </c>
       <c r="J283" t="n">
-        <v>27.4797</v>
+        <v>24.9223</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.61</v>
       </c>
       <c r="I284" t="n">
-        <v>1.2921</v>
+        <v>1.2198</v>
       </c>
       <c r="J284" t="n">
-        <v>24.5499</v>
+        <v>23.1762</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.41</v>
       </c>
       <c r="I285" t="n">
-        <v>0.8448</v>
+        <v>0.969</v>
       </c>
       <c r="J285" t="n">
-        <v>16.0512</v>
+        <v>18.411</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4334</v>
+        <v>-0.3498</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.2346</v>
+        <v>-6.6462</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.92</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0163</v>
+        <v>-0.0475</v>
       </c>
       <c r="J287" t="n">
-        <v>-0.3097</v>
+        <v>-0.9025</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0341</v>
+        <v>-0.0604</v>
       </c>
       <c r="J288" t="n">
-        <v>-0.6479</v>
+        <v>-1.1476</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.5555</v>
+        <v>-0.3816</v>
       </c>
       <c r="J289" t="n">
-        <v>-10.5545</v>
+        <v>-7.2504</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.54</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6434</v>
+        <v>-0.4374</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.2246</v>
+        <v>-8.310600000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.3</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.95</v>
+        <v>-0.6636</v>
       </c>
       <c r="J291" t="n">
-        <v>-18.05</v>
+        <v>-12.6084</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.9219</v>
+        <v>1.6304</v>
       </c>
       <c r="J292" t="n">
-        <v>36.5161</v>
+        <v>30.9776</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.84</v>
       </c>
       <c r="I293" t="n">
-        <v>1.6792</v>
+        <v>1.4662</v>
       </c>
       <c r="J293" t="n">
-        <v>31.9048</v>
+        <v>27.8578</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.7</v>
       </c>
       <c r="I294" t="n">
-        <v>1.4223</v>
+        <v>1.3109</v>
       </c>
       <c r="J294" t="n">
-        <v>27.0237</v>
+        <v>24.9071</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>0.9118000000000001</v>
+        <v>1.0349</v>
       </c>
       <c r="J295" t="n">
-        <v>17.3242</v>
+        <v>19.6631</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0253</v>
+        <v>0.0655</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.4807</v>
+        <v>1.2445</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.73</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.264</v>
+        <v>-0.2295</v>
       </c>
       <c r="J297" t="n">
-        <v>-5.016</v>
+        <v>-4.3605</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.64</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.4021</v>
+        <v>-0.3249</v>
       </c>
       <c r="J298" t="n">
-        <v>-7.6399</v>
+        <v>-6.1731</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4177</v>
+        <v>-0.335</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.9363</v>
+        <v>-6.365</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.8253</v>
+        <v>-0.5692</v>
       </c>
       <c r="J300" t="n">
-        <v>-15.6807</v>
+        <v>-10.8148</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8521</v>
+        <v>-0.5887</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.1899</v>
+        <v>-11.1853</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.41</v>
       </c>
       <c r="I302" t="n">
-        <v>1.0544</v>
+        <v>1.0302</v>
       </c>
       <c r="J302" t="n">
-        <v>36.904</v>
+        <v>36.057</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.39</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0118</v>
+        <v>0.9977</v>
       </c>
       <c r="J303" t="n">
-        <v>35.413</v>
+        <v>34.9195</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.2</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5621</v>
+        <v>0.5658</v>
       </c>
       <c r="J304" t="n">
-        <v>19.6735</v>
+        <v>19.803</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2487</v>
+        <v>-0.1733</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.704499999999999</v>
+        <v>-6.0655</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5727</v>
+        <v>-0.5074</v>
       </c>
       <c r="J306" t="n">
-        <v>-20.0445</v>
+        <v>-17.759</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.51</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7876</v>
+        <v>0.9807</v>
       </c>
       <c r="J307" t="n">
-        <v>27.566</v>
+        <v>34.3245</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.99</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.42</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.92</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1788</v>
+        <v>-0.1079</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.258</v>
+        <v>-3.7765</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.8</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3747</v>
+        <v>-0.2348</v>
       </c>
       <c r="J310" t="n">
-        <v>-13.1145</v>
+        <v>-8.218</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6404</v>
+        <v>-0.4254</v>
       </c>
       <c r="J311" t="n">
-        <v>-22.414</v>
+        <v>-14.889</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.38</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9903</v>
+        <v>0.9796</v>
       </c>
       <c r="J312" t="n">
-        <v>27.7284</v>
+        <v>27.4288</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7163</v>
+        <v>0.7097</v>
       </c>
       <c r="J313" t="n">
-        <v>20.0564</v>
+        <v>19.8716</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.25</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6917</v>
+        <v>0.6859</v>
       </c>
       <c r="J314" t="n">
-        <v>19.3676</v>
+        <v>19.2052</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2544</v>
+        <v>0.3103</v>
       </c>
       <c r="J315" t="n">
-        <v>7.1232</v>
+        <v>8.6884</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6236</v>
+        <v>-0.5616</v>
       </c>
       <c r="J316" t="n">
-        <v>-17.4608</v>
+        <v>-15.7248</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4317</v>
+        <v>0.4957</v>
       </c>
       <c r="J317" t="n">
-        <v>12.0876</v>
+        <v>13.8796</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3446</v>
+        <v>0.3823</v>
       </c>
       <c r="J318" t="n">
-        <v>9.6488</v>
+        <v>10.7044</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1692</v>
+        <v>-0.1059</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.7376</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3544</v>
+        <v>-0.2223</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.9232</v>
+        <v>-6.2244</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6248</v>
+        <v>-0.414</v>
       </c>
       <c r="J321" t="n">
-        <v>-17.4944</v>
+        <v>-11.592</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3714/event_3714_evp_summary.xlsx
+++ b/database/event/3714/event_3714_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.938</v>
+        <v>5.99</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9247</v>
+        <v>0.9328</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0427</v>
+        <v>2.1026</v>
       </c>
       <c r="E2" t="n">
-        <v>5.938</v>
+        <v>5.99</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0523</v>
+        <v>2.946</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8857</v>
+        <v>3.044</v>
       </c>
       <c r="H2" t="n">
-        <v>5.268</v>
+        <v>4.8258</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7391</v>
+        <v>2.6059</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8857</v>
+        <v>3.044</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>114</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6248</v>
+        <v>5.649900000000001</v>
       </c>
       <c r="N2" t="n">
         <v>255</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8619</v>
+        <v>5.7807</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9002</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0083</v>
+        <v>2.0073</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8619</v>
+        <v>5.7807</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0907</v>
+        <v>2.7312</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7713</v>
+        <v>3.0495</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4268</v>
+        <v>3.2529</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4268</v>
+        <v>3.2529</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7713</v>
+        <v>3.0495</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1981</v>
+        <v>6.3024</v>
       </c>
       <c r="N3" t="n">
         <v>254</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7977</v>
+        <v>4.8647</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7471</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5279</v>
+        <v>1.5903</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7977</v>
+        <v>4.8647</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7371</v>
+        <v>3.6491</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0606</v>
+        <v>1.2156</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6809</v>
+        <v>7.1455</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9937</v>
+        <v>3.8585</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0606</v>
+        <v>1.2156</v>
       </c>
       <c r="K4" t="n">
         <v>139</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0543</v>
+        <v>5.0741</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5153</v>
+        <v>4.6199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7194</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4004</v>
+        <v>1.4789</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5153</v>
+        <v>4.6199</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1102</v>
+        <v>1.9724</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4051</v>
+        <v>2.6475</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1102</v>
+        <v>1.9724</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0972</v>
+        <v>1.0651</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4051</v>
+        <v>2.6475</v>
       </c>
       <c r="K5" t="n">
         <v>139</v>
@@ -667,7 +667,7 @@
         <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5023</v>
+        <v>3.7126</v>
       </c>
       <c r="N5" t="n">
         <v>256</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4498</v>
+        <v>4.2811</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6929</v>
+        <v>0.6667</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3708</v>
+        <v>1.3246</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4498</v>
+        <v>4.2811</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4977</v>
+        <v>3.2057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.0754</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3206</v>
+        <v>4.2913</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4983</v>
+        <v>4.4019</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.0754</v>
       </c>
       <c r="K6" t="n">
         <v>114</v>
@@ -713,7 +713,7 @@
         <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4504</v>
+        <v>5.477300000000001</v>
       </c>
       <c r="N6" t="n">
         <v>190</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1413</v>
+        <v>4.0916</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6449</v>
+        <v>0.6372</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2316</v>
+        <v>1.2384</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1413</v>
+        <v>4.0916</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6633</v>
+        <v>3.5551</v>
       </c>
       <c r="G7" t="n">
-        <v>0.478</v>
+        <v>0.5365</v>
       </c>
       <c r="H7" t="n">
-        <v>7.421</v>
+        <v>6.8353</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8586</v>
+        <v>3.691</v>
       </c>
       <c r="J7" t="n">
-        <v>0.478</v>
+        <v>0.5365</v>
       </c>
       <c r="K7" t="n">
         <v>139</v>
@@ -759,7 +759,7 @@
         <v>117</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3366</v>
+        <v>4.2275</v>
       </c>
       <c r="N7" t="n">
         <v>256</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8192</v>
+        <v>3.6576</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5947</v>
+        <v>0.5696</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0862</v>
+        <v>1.0408</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8192</v>
+        <v>3.6576</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9524</v>
+        <v>2.6837</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8668</v>
+        <v>0.9739</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1233</v>
+        <v>3.1489</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2517</v>
+        <v>3.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8668</v>
+        <v>0.9739</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1185</v>
+        <v>4.2039</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -824,25 +824,25 @@
         <v>0.4806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7552</v>
+        <v>0.7806</v>
       </c>
       <c r="E9" t="n">
         <v>3.086</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0756</v>
+        <v>1.9739</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0104</v>
+        <v>1.1121</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0756</v>
+        <v>1.9739</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0756</v>
+        <v>1.9739</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0104</v>
+        <v>1.1121</v>
       </c>
       <c r="K9" t="n">
         <v>116</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9035</v>
+        <v>2.915</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4521</v>
+        <v>0.4539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6728</v>
+        <v>0.7028</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9035</v>
+        <v>2.915</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7307</v>
+        <v>1.6485</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1728</v>
+        <v>1.2665</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7307</v>
+        <v>1.6485</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7307</v>
+        <v>1.6485</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1728</v>
+        <v>1.2665</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9035</v>
+        <v>2.915</v>
       </c>
       <c r="N10" t="n">
         <v>203</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8854</v>
+        <v>2.847</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4493</v>
+        <v>0.4433</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6646</v>
+        <v>0.6718</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8854</v>
+        <v>2.847</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8604</v>
+        <v>1.736</v>
       </c>
       <c r="G11" t="n">
-        <v>1.025</v>
+        <v>1.111</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8604</v>
+        <v>1.736</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9673</v>
+        <v>0.9374</v>
       </c>
       <c r="J11" t="n">
-        <v>1.025</v>
+        <v>1.111</v>
       </c>
       <c r="K11" t="n">
         <v>141</v>
@@ -943,7 +943,7 @@
         <v>114</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9923</v>
+        <v>2.0484</v>
       </c>
       <c r="N11" t="n">
         <v>255</v>
@@ -952,127 +952,127 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8095</v>
+        <v>2.8416</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4375</v>
+        <v>0.4425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6303</v>
+        <v>0.6694</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8095</v>
+        <v>2.8416</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3351</v>
+        <v>2.1314</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5256</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2646</v>
+        <v>2.1314</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2573</v>
+        <v>2.1863</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5256</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L12" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7317</v>
+        <v>2.8965</v>
       </c>
       <c r="N12" t="n">
-        <v>255</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7067</v>
+        <v>2.7349</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4215</v>
+        <v>0.4259</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5839</v>
+        <v>0.6208</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7067</v>
+        <v>2.7349</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1334</v>
+        <v>3.2143</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5733</v>
+        <v>-0.4794</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1334</v>
+        <v>5.7108</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2211</v>
+        <v>3.0838</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5733</v>
+        <v>-0.4794</v>
       </c>
       <c r="K13" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7944</v>
+        <v>2.6044</v>
       </c>
       <c r="N13" t="n">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.666</v>
+        <v>2.6744</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4152</v>
+        <v>0.4165</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5656</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.666</v>
+        <v>2.6744</v>
       </c>
       <c r="F14" t="n">
-        <v>2.204</v>
+        <v>0.4224</v>
       </c>
       <c r="G14" t="n">
-        <v>0.462</v>
+        <v>2.252</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2792</v>
+        <v>0.4224</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1851</v>
+        <v>0.2281</v>
       </c>
       <c r="J14" t="n">
-        <v>0.462</v>
+        <v>2.252</v>
       </c>
       <c r="K14" t="n">
         <v>141</v>
@@ -1081,7 +1081,7 @@
         <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6471</v>
+        <v>2.4801</v>
       </c>
       <c r="N14" t="n">
         <v>255</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5015</v>
+        <v>2.6047</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3895</v>
+        <v>0.4056</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4913</v>
+        <v>0.5615</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5015</v>
+        <v>2.6047</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4083</v>
+        <v>2.1455</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0932</v>
+        <v>0.4592</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4083</v>
+        <v>2.1847</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2123</v>
+        <v>1.1797</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0932</v>
+        <v>0.4592</v>
       </c>
       <c r="K15" t="n">
         <v>141</v>
@@ -1127,7 +1127,7 @@
         <v>114</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3055</v>
+        <v>1.6389</v>
       </c>
       <c r="N15" t="n">
         <v>255</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3649</v>
+        <v>2.5302</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3683</v>
+        <v>0.394</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4296</v>
+        <v>0.5276</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3649</v>
+        <v>2.5302</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9556</v>
+        <v>-0.9117</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4093</v>
+        <v>3.4419</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9556</v>
+        <v>-0.9117</v>
       </c>
       <c r="I16" t="n">
-        <v>2.036</v>
+        <v>-0.4923</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4093</v>
+        <v>3.4419</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L16" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4453</v>
+        <v>2.9496</v>
       </c>
       <c r="N16" t="n">
-        <v>190</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2637</v>
+        <v>2.432</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3525</v>
+        <v>0.3787</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3839</v>
+        <v>0.4829</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2637</v>
+        <v>2.432</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0336</v>
+        <v>1.9555</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2973</v>
+        <v>0.4765</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0336</v>
+        <v>1.9555</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5374</v>
+        <v>2.0059</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2973</v>
+        <v>0.4765</v>
       </c>
       <c r="K17" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L17" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7599</v>
+        <v>2.4824</v>
       </c>
       <c r="N17" t="n">
-        <v>256</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1695</v>
+        <v>1.9845</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3378</v>
+        <v>0.309</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3414</v>
+        <v>0.2792</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1695</v>
+        <v>1.9845</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4949</v>
+        <v>2.322</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3254</v>
+        <v>-0.3375</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4949</v>
+        <v>2.3573</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4949</v>
+        <v>2.3573</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3254</v>
+        <v>-0.3375</v>
       </c>
       <c r="K18" t="n">
         <v>121</v>
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1695</v>
+        <v>2.0198</v>
       </c>
       <c r="N18" t="n">
         <v>203</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8241</v>
+        <v>1.8884</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2841</v>
+        <v>0.2941</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1855</v>
+        <v>0.2354</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8241</v>
+        <v>1.8884</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4703</v>
+        <v>1.8635</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3538</v>
+        <v>0.0249</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4703</v>
+        <v>1.8635</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4703</v>
+        <v>1.9115</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3538</v>
+        <v>0.0249</v>
       </c>
       <c r="K19" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="L19" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8241</v>
+        <v>1.9364</v>
       </c>
       <c r="N19" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.812</v>
+        <v>1.8033</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2822</v>
+        <v>0.2808</v>
       </c>
       <c r="D20" t="n">
-        <v>0.18</v>
+        <v>0.1967</v>
       </c>
       <c r="E20" t="n">
-        <v>1.812</v>
+        <v>1.8033</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8568</v>
+        <v>1.3873</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0448</v>
+        <v>0.416</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8568</v>
+        <v>1.3873</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9332</v>
+        <v>1.3873</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0448</v>
+        <v>0.416</v>
       </c>
       <c r="K20" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8884</v>
+        <v>1.8033</v>
       </c>
       <c r="N20" t="n">
-        <v>274</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3931</v>
+        <v>1.2705</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2169</v>
+        <v>0.1978</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0091</v>
+        <v>-0.0458</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3931</v>
+        <v>1.2705</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9547</v>
+        <v>1.873</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5616</v>
+        <v>-0.6025</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9547</v>
+        <v>1.873</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9547</v>
+        <v>1.873</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5616</v>
+        <v>-0.6025</v>
       </c>
       <c r="K21" t="n">
         <v>121</v>
@@ -1403,7 +1403,7 @@
         <v>82</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3931</v>
+        <v>1.2705</v>
       </c>
       <c r="N21" t="n">
         <v>203</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1861</v>
+        <v>1.2618</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1847</v>
+        <v>0.1965</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1025</v>
+        <v>-0.0498</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1861</v>
+        <v>1.2618</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4637</v>
+        <v>0.4729</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2776</v>
+        <v>0.7889</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4637</v>
+        <v>0.4729</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4637</v>
+        <v>0.4851</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2776</v>
+        <v>0.7889</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1861</v>
+        <v>1.274</v>
       </c>
       <c r="N22" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1777</v>
+        <v>1.1116</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1834</v>
+        <v>0.1731</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1063</v>
+        <v>-0.1182</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1777</v>
+        <v>1.1116</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4603</v>
+        <v>0.7664</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7174</v>
+        <v>0.3452</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4603</v>
+        <v>0.7664</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4792</v>
+        <v>0.7862</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7174</v>
+        <v>0.3452</v>
       </c>
       <c r="K23" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L23" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1966</v>
+        <v>1.1314</v>
       </c>
       <c r="N23" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0792</v>
+        <v>1.0391</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1681</v>
+        <v>0.1618</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1508</v>
+        <v>-0.1512</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0792</v>
+        <v>1.0391</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7504999999999999</v>
+        <v>1.3312</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3287</v>
+        <v>-0.2921</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7504999999999999</v>
+        <v>1.3312</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7814</v>
+        <v>1.3312</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3287</v>
+        <v>-0.2921</v>
       </c>
       <c r="K24" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1101</v>
+        <v>1.0391</v>
       </c>
       <c r="N24" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.0094</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1542</v>
+        <v>0.1572</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1909</v>
+        <v>-0.1647</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.0094</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3468</v>
+        <v>1.3691</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3564</v>
+        <v>-0.3597</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3468</v>
+        <v>1.3691</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4022</v>
+        <v>1.4044</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3564</v>
+        <v>-0.3597</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0458</v>
+        <v>1.0447</v>
       </c>
       <c r="N25" t="n">
         <v>190</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1383</v>
+        <v>0.1318</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2372</v>
+        <v>-0.239</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8879</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0954</v>
+        <v>0.0916</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3616</v>
+        <v>-0.3563</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6123</v>
+        <v>0.5885</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3562</v>
+        <v>0.3849</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0555</v>
+        <v>0.0599</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4772</v>
+        <v>-0.449</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3562</v>
+        <v>0.3849</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7597</v>
+        <v>0.7454</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4035</v>
+        <v>-0.3605</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7597</v>
+        <v>0.7454</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7597</v>
+        <v>0.7454</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4035</v>
+        <v>-0.3605</v>
       </c>
       <c r="K28" t="n">
         <v>116</v>
@@ -1725,7 +1725,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3562</v>
+        <v>0.3849</v>
       </c>
       <c r="N28" t="n">
         <v>254</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0092</v>
+        <v>0.005</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6112</v>
+        <v>-0.6095</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0593</v>
+        <v>0.0324</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0019</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6435</v>
+        <v>-0.6532</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0121</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.012</v>
+        <v>-0.0179</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6727</v>
+        <v>-0.6765</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1149</v>
       </c>
       <c r="N31" t="n">
         <v>125</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.336</v>
+        <v>-0.3646</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0523</v>
+        <v>-0.0568</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7897</v>
+        <v>-0.7902</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.336</v>
+        <v>-0.3646</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.336</v>
+        <v>-0.4823</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.1177</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.336</v>
+        <v>-0.4823</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.336</v>
+        <v>-0.4947</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.1177</v>
       </c>
       <c r="K32" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.336</v>
+        <v>-0.377</v>
       </c>
       <c r="N32" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3819</v>
+        <v>-0.4019</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0595</v>
+        <v>-0.0626</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8104</v>
+        <v>-0.8072</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3819</v>
+        <v>-0.4019</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4806</v>
+        <v>-0.4019</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0987</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4806</v>
+        <v>-0.4019</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5004</v>
+        <v>-0.4019</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0987</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="L33" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4016999999999999</v>
+        <v>-0.4019</v>
       </c>
       <c r="N33" t="n">
-        <v>274</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0595</v>
+        <v>-0.0668</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8105</v>
+        <v>-0.8196</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3821</v>
+        <v>-0.4292</v>
       </c>
       <c r="N34" t="n">
         <v>125</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4325</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0794</v>
+        <v>-0.0674</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8681</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4325</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-1.0976</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-1.0976</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5927</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.07240000000000002</v>
       </c>
       <c r="N35" t="n">
-        <v>91</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5926</v>
+        <v>-0.5623</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0876</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9055</v>
+        <v>-0.8802</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5926</v>
+        <v>-0.5623</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2895</v>
+        <v>-0.5623</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6969</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2895</v>
+        <v>-0.5623</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6705</v>
+        <v>-0.5623</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6969</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="L36" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.02639999999999998</v>
+        <v>-0.5623</v>
       </c>
       <c r="N36" t="n">
-        <v>256</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6864</v>
+        <v>-0.6469</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1069</v>
+        <v>-0.1007</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9479</v>
+        <v>-0.9187</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6864</v>
+        <v>-0.6469</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4394</v>
+        <v>-0.4486</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.247</v>
+        <v>-0.1983</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4394</v>
+        <v>-0.4486</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4394</v>
+        <v>-0.4486</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.247</v>
+        <v>-0.1983</v>
       </c>
       <c r="K37" t="n">
         <v>116</v>
@@ -2139,7 +2139,7 @@
         <v>138</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6864</v>
+        <v>-0.6469</v>
       </c>
       <c r="N37" t="n">
         <v>254</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9387</v>
+        <v>-0.861</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1462</v>
+        <v>-0.1341</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0618</v>
+        <v>-1.0161</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9387</v>
+        <v>-0.861</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2911</v>
+        <v>-1.2559</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3524</v>
+        <v>0.3949</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2911</v>
+        <v>-1.2559</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2911</v>
+        <v>-1.2559</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3524</v>
+        <v>0.3949</v>
       </c>
       <c r="K38" t="n">
         <v>116</v>
@@ -2185,7 +2185,7 @@
         <v>138</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9386999999999999</v>
+        <v>-0.861</v>
       </c>
       <c r="N38" t="n">
         <v>254</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1525</v>
+        <v>-0.1635</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0802</v>
+        <v>-1.1022</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9794</v>
+        <v>-1.05</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2651</v>
+        <v>-0.269</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4065</v>
+        <v>-1.4105</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7023</v>
+        <v>-1.7273</v>
       </c>
       <c r="N40" t="n">
         <v>91</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3562</v>
+        <v>-2.3559</v>
       </c>
       <c r="C41" t="n">
         <v>-0.3669</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7017</v>
+        <v>-1.6967</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3562</v>
+        <v>-2.3559</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2246</v>
+        <v>-1.2244</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.1316</v>
+        <v>-1.1315</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2246</v>
+        <v>-1.2244</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.275</v>
+        <v>-1.256</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1316</v>
+        <v>-1.1315</v>
       </c>
       <c r="K41" t="n">
         <v>145</v>
@@ -2323,7 +2323,7 @@
         <v>129</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4066</v>
+        <v>-2.3875</v>
       </c>
       <c r="N41" t="n">
         <v>274</v>
@@ -2429,10 +2429,10 @@
         <v>1.87</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9355</v>
+        <v>0.9246</v>
       </c>
       <c r="J2" t="n">
-        <v>17.7745</v>
+        <v>17.5674</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6966</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>13.2354</v>
+        <v>13.3399</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.58</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>11.02</v>
+        <v>11.2518</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.49</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5699</v>
+        <v>0.5826</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8281</v>
+        <v>11.0694</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3305</v>
+        <v>0.3542</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2795</v>
+        <v>6.7298</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3812</v>
+        <v>0.3505</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2428</v>
+        <v>6.6595</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1356</v>
+        <v>-0.1632</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5764</v>
+        <v>-3.1008</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.48</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4891</v>
+        <v>-0.5018</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.292899999999999</v>
+        <v>-9.5342</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.38</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5839</v>
+        <v>-0.5897</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.0941</v>
+        <v>-11.2043</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.32</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6411</v>
+        <v>-0.6423</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.1809</v>
+        <v>-12.2037</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2161</v>
+        <v>0.1979</v>
       </c>
       <c r="J12" t="n">
-        <v>4.322</v>
+        <v>3.958</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.93</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0606</v>
+        <v>-0.081</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.212</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.274</v>
+        <v>-0.2937</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.48</v>
+        <v>-5.874</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4231</v>
+        <v>-0.437</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.462</v>
+        <v>-8.74</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5718</v>
+        <v>-0.5764</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.436</v>
+        <v>-11.528</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5122</v>
+        <v>1.6488</v>
       </c>
       <c r="J17" t="n">
-        <v>30.244</v>
+        <v>32.976</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.283</v>
+        <v>1.3584</v>
       </c>
       <c r="J18" t="n">
-        <v>25.66</v>
+        <v>27.168</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8091</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>16.182</v>
+        <v>15.534</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6494</v>
+        <v>0.6358</v>
       </c>
       <c r="J20" t="n">
-        <v>12.988</v>
+        <v>12.716</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6258</v>
+        <v>0.6149</v>
       </c>
       <c r="J21" t="n">
-        <v>12.516</v>
+        <v>12.298</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.699</v>
+        <v>0.6637</v>
       </c>
       <c r="J22" t="n">
-        <v>15.378</v>
+        <v>14.6014</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1242</v>
+        <v>-0.1393</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7324</v>
+        <v>-3.0646</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.88</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.145</v>
+        <v>-0.1608</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.19</v>
+        <v>-3.5376</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.72</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3048</v>
+        <v>-0.3194</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.7056</v>
+        <v>-7.0268</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3524</v>
+        <v>-0.3655</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.7528</v>
+        <v>-8.041</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.531</v>
+        <v>1.6579</v>
       </c>
       <c r="J27" t="n">
-        <v>33.682</v>
+        <v>36.4738</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7872</v>
+        <v>0.7486</v>
       </c>
       <c r="J28" t="n">
-        <v>17.3184</v>
+        <v>16.4692</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.432</v>
+        <v>0.4301</v>
       </c>
       <c r="J29" t="n">
-        <v>9.504</v>
+        <v>9.462199999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2886</v>
+        <v>-0.272</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.3492</v>
+        <v>-5.984</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3802</v>
+        <v>-0.3573</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.3644</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7388</v>
+        <v>0.8149</v>
       </c>
       <c r="J32" t="n">
-        <v>21.4252</v>
+        <v>23.6321</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4889</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>14.1781</v>
+        <v>15.6542</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4008</v>
+        <v>0.4375</v>
       </c>
       <c r="J34" t="n">
-        <v>11.6232</v>
+        <v>12.6875</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1992</v>
+        <v>0.2101</v>
       </c>
       <c r="J35" t="n">
-        <v>5.7768</v>
+        <v>6.0929</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4446</v>
+        <v>-0.4212</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.8934</v>
+        <v>-12.2148</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2634</v>
+        <v>0.2649</v>
       </c>
       <c r="J37" t="n">
-        <v>7.6386</v>
+        <v>7.6821</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0785</v>
+        <v>0.0823</v>
       </c>
       <c r="J38" t="n">
-        <v>2.2765</v>
+        <v>2.3867</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0493</v>
+        <v>0.0516</v>
       </c>
       <c r="J39" t="n">
-        <v>1.4297</v>
+        <v>1.4964</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1386</v>
+        <v>-0.1531</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.0194</v>
+        <v>-4.4399</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3482</v>
+        <v>-0.3605</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.0978</v>
+        <v>-10.4545</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7012</v>
+        <v>0.7734</v>
       </c>
       <c r="J42" t="n">
-        <v>18.9324</v>
+        <v>20.8818</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6464</v>
+        <v>0.7136</v>
       </c>
       <c r="J43" t="n">
-        <v>17.4528</v>
+        <v>19.2672</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2326</v>
+        <v>0.2409</v>
       </c>
       <c r="J44" t="n">
-        <v>6.2802</v>
+        <v>6.5043</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1628</v>
+        <v>-0.1581</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.3956</v>
+        <v>-4.2687</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.355</v>
+        <v>-0.3397</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.585000000000001</v>
+        <v>-9.171900000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5687</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>15.3549</v>
+        <v>16.9965</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0827</v>
+        <v>-0.0949</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.2329</v>
+        <v>-2.5623</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1274</v>
+        <v>-0.1416</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.4398</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2806</v>
+        <v>-0.2949</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.5762</v>
+        <v>-7.9623</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2903</v>
+        <v>-0.3044</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.8381</v>
+        <v>-8.2188</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2664</v>
+        <v>1.3827</v>
       </c>
       <c r="J52" t="n">
-        <v>36.7256</v>
+        <v>40.0983</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9764</v>
+        <v>1.0764</v>
       </c>
       <c r="J53" t="n">
-        <v>28.3156</v>
+        <v>31.2156</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2281</v>
+        <v>0.245</v>
       </c>
       <c r="J54" t="n">
-        <v>6.6149</v>
+        <v>7.105</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3309</v>
+        <v>-0.3091</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.5961</v>
+        <v>-8.963900000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4203</v>
+        <v>-0.3919</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.1887</v>
+        <v>-11.3651</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2482</v>
+        <v>0.249</v>
       </c>
       <c r="J57" t="n">
-        <v>7.1978</v>
+        <v>7.221</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2267</v>
+        <v>0.2282</v>
       </c>
       <c r="J58" t="n">
-        <v>6.5743</v>
+        <v>6.6178</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0148</v>
+        <v>0.0106</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4292</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1891</v>
+        <v>-0.2048</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.4839</v>
+        <v>-5.9392</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4206</v>
+        <v>-0.4304</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.1974</v>
+        <v>-12.4816</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.55</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9099</v>
+        <v>1.0061</v>
       </c>
       <c r="J62" t="n">
-        <v>21.8376</v>
+        <v>24.1464</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.45</v>
       </c>
       <c r="I63" t="n">
-        <v>0.785</v>
+        <v>0.8716</v>
       </c>
       <c r="J63" t="n">
-        <v>18.84</v>
+        <v>20.9184</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6832</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>16.3968</v>
+        <v>18.2544</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3514</v>
+        <v>0.3713</v>
       </c>
       <c r="J65" t="n">
-        <v>8.4336</v>
+        <v>8.911199999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.96</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2393</v>
+        <v>-0.221</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.7432</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1391</v>
+        <v>0.1266</v>
       </c>
       <c r="J67" t="n">
-        <v>3.3384</v>
+        <v>3.0384</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1066</v>
+        <v>-0.1257</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.5584</v>
+        <v>-3.0168</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.326</v>
+        <v>-0.3432</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.824</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3449</v>
+        <v>-0.3613</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.2776</v>
+        <v>-8.671200000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3825</v>
+        <v>-0.3973</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.18</v>
+        <v>-9.5352</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6734</v>
+        <v>0.7462</v>
       </c>
       <c r="J72" t="n">
-        <v>16.835</v>
+        <v>18.655</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.29</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5924</v>
+        <v>0.6572</v>
       </c>
       <c r="J73" t="n">
-        <v>14.81</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.2</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4678</v>
+        <v>0.5179</v>
       </c>
       <c r="J74" t="n">
-        <v>11.695</v>
+        <v>12.9475</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3488</v>
+        <v>0.3624</v>
       </c>
       <c r="J75" t="n">
-        <v>8.720000000000001</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0466</v>
+        <v>-0.0322</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.165</v>
+        <v>-0.805</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.5</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7244</v>
+        <v>0.8026</v>
       </c>
       <c r="J77" t="n">
-        <v>18.11</v>
+        <v>20.065</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.126</v>
+        <v>-0.1406</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.15</v>
+        <v>-3.515</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2196</v>
+        <v>-0.2351</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.49</v>
+        <v>-5.8775</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2196</v>
+        <v>-0.2351</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.49</v>
+        <v>-5.8775</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.59</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4298</v>
+        <v>-0.4392</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.745</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6994</v>
+        <v>0.7861</v>
       </c>
       <c r="J82" t="n">
-        <v>19.5832</v>
+        <v>22.0108</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4763</v>
+        <v>0.5326</v>
       </c>
       <c r="J83" t="n">
-        <v>13.3364</v>
+        <v>14.9128</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.87</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.172</v>
+        <v>-0.1842</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.816</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.388</v>
+        <v>-0.3968</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.864</v>
+        <v>-11.1104</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4156</v>
+        <v>-0.4233</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.6368</v>
+        <v>-11.8524</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3713</v>
+        <v>0.409</v>
       </c>
       <c r="J87" t="n">
-        <v>10.3964</v>
+        <v>11.452</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2756</v>
+        <v>0.2917</v>
       </c>
       <c r="J88" t="n">
-        <v>7.7168</v>
+        <v>8.1676</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2631</v>
+        <v>0.2794</v>
       </c>
       <c r="J89" t="n">
-        <v>7.3668</v>
+        <v>7.8232</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2251</v>
+        <v>0.2418</v>
       </c>
       <c r="J90" t="n">
-        <v>6.3028</v>
+        <v>6.7704</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1816</v>
+        <v>-0.1917</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.0848</v>
+        <v>-5.3676</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.68</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0923</v>
+        <v>1.1963</v>
       </c>
       <c r="J92" t="n">
-        <v>31.6767</v>
+        <v>34.6927</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6441</v>
+        <v>0.7147</v>
       </c>
       <c r="J93" t="n">
-        <v>18.6789</v>
+        <v>20.7263</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3266</v>
+        <v>0.335</v>
       </c>
       <c r="J94" t="n">
-        <v>9.471399999999999</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.96</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2185</v>
+        <v>-0.2064</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.3365</v>
+        <v>-5.9856</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.252</v>
+        <v>-0.2383</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.308</v>
+        <v>-6.9107</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4123</v>
+        <v>0.4462</v>
       </c>
       <c r="J97" t="n">
-        <v>11.9567</v>
+        <v>12.9398</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1728</v>
+        <v>0.1722</v>
       </c>
       <c r="J98" t="n">
-        <v>5.0112</v>
+        <v>4.9938</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.254</v>
+        <v>-0.2702</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.366</v>
+        <v>-7.8358</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2831</v>
+        <v>-0.2988</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.209899999999999</v>
+        <v>-8.6652</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3689</v>
+        <v>-0.3818</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.6981</v>
+        <v>-11.0722</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4073</v>
+        <v>0.4469</v>
       </c>
       <c r="J102" t="n">
-        <v>12.219</v>
+        <v>13.407</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="J103" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0629</v>
+        <v>-0.0722</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.887</v>
+        <v>-2.166</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.91</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1226</v>
+        <v>-0.1351</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.678</v>
+        <v>-4.053</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1338</v>
+        <v>-0.1466</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.014</v>
+        <v>-4.398</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8208</v>
+        <v>0.9031</v>
       </c>
       <c r="J107" t="n">
-        <v>24.624</v>
+        <v>27.093</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6178</v>
+        <v>0.6825</v>
       </c>
       <c r="J108" t="n">
-        <v>18.534</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3717</v>
+        <v>0.3947</v>
       </c>
       <c r="J109" t="n">
-        <v>11.151</v>
+        <v>11.841</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2645</v>
+        <v>-0.2551</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.935</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.579</v>
+        <v>-0.5429</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.37</v>
+        <v>-16.287</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.96</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7468</v>
+        <v>0.8626</v>
       </c>
       <c r="J112" t="n">
-        <v>15.6828</v>
+        <v>18.1146</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.69</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5927</v>
+        <v>0.6851</v>
       </c>
       <c r="J113" t="n">
-        <v>12.4467</v>
+        <v>14.3871</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.65</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5694</v>
+        <v>0.658</v>
       </c>
       <c r="J114" t="n">
-        <v>11.9574</v>
+        <v>13.818</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1207</v>
+        <v>0.1462</v>
       </c>
       <c r="J115" t="n">
-        <v>2.5347</v>
+        <v>3.0702</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0427</v>
+        <v>-0.0333</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.6993</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3066</v>
+        <v>0.2871</v>
       </c>
       <c r="J117" t="n">
-        <v>6.4386</v>
+        <v>6.0291</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0162</v>
+        <v>-0.0102</v>
       </c>
       <c r="J118" t="n">
-        <v>0.3402</v>
+        <v>-0.2142</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4236</v>
+        <v>-0.4389</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.8956</v>
+        <v>-9.216900000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5173</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.8633</v>
+        <v>-11.0607</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6484</v>
+        <v>-0.6481</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.6164</v>
+        <v>-13.6101</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3306</v>
+        <v>0.3341</v>
       </c>
       <c r="J122" t="n">
-        <v>8.265000000000001</v>
+        <v>8.352499999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2538</v>
+        <v>0.2579</v>
       </c>
       <c r="J123" t="n">
-        <v>6.345</v>
+        <v>6.4475</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0479</v>
+        <v>-0.0566</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.1975</v>
+        <v>-1.415</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1093</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.43</v>
+        <v>-2.7325</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.314</v>
+        <v>-0.3266</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.85</v>
+        <v>-8.164999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9151</v>
+        <v>1.0084</v>
       </c>
       <c r="J127" t="n">
-        <v>22.8775</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6427</v>
+        <v>0.7135</v>
       </c>
       <c r="J128" t="n">
-        <v>16.0675</v>
+        <v>17.8375</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.3</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6025</v>
+        <v>0.6691</v>
       </c>
       <c r="J129" t="n">
-        <v>15.0625</v>
+        <v>16.7275</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2205</v>
+        <v>-0.2078</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.5125</v>
+        <v>-5.195</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2862</v>
+        <v>-0.2702</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.155</v>
+        <v>-6.755</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.38</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7174</v>
+        <v>0.694</v>
       </c>
       <c r="J132" t="n">
-        <v>21.522</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3585</v>
+        <v>0.3641</v>
       </c>
       <c r="J133" t="n">
-        <v>10.755</v>
+        <v>10.923</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.322</v>
+        <v>0.3296</v>
       </c>
       <c r="J134" t="n">
-        <v>9.66</v>
+        <v>9.888</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0598</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.794</v>
+        <v>-1.971</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2297</v>
+        <v>-0.2409</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.891</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.17</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5119</v>
       </c>
       <c r="J137" t="n">
-        <v>16.044</v>
+        <v>15.357</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3139</v>
+        <v>0.3111</v>
       </c>
       <c r="J138" t="n">
-        <v>9.417</v>
+        <v>9.333</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2239</v>
+        <v>0.2269</v>
       </c>
       <c r="J139" t="n">
-        <v>6.717</v>
+        <v>6.807</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.354</v>
+        <v>-0.3456</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.62</v>
+        <v>-10.368</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4389</v>
+        <v>-0.423</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.167</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.18</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3918</v>
+        <v>0.3921</v>
       </c>
       <c r="J142" t="n">
-        <v>11.754</v>
+        <v>11.763</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3918</v>
+        <v>0.3921</v>
       </c>
       <c r="J143" t="n">
-        <v>11.754</v>
+        <v>11.763</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0794</v>
+        <v>-0.0887</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.382</v>
+        <v>-2.661</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0794</v>
+        <v>-0.0887</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.382</v>
+        <v>-2.661</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1268</v>
+        <v>-0.1383</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.804</v>
+        <v>-4.149</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3873</v>
+        <v>1.3584</v>
       </c>
       <c r="J147" t="n">
-        <v>41.619</v>
+        <v>40.752</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1823</v>
+        <v>0.1902</v>
       </c>
       <c r="J148" t="n">
-        <v>5.469</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.079</v>
+        <v>0.0896</v>
       </c>
       <c r="J149" t="n">
-        <v>2.37</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5638</v>
+        <v>-0.5322</v>
       </c>
       <c r="J150" t="n">
-        <v>-16.914</v>
+        <v>-15.966</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6166</v>
+        <v>-0.5793</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.498</v>
+        <v>-17.379</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4096</v>
+        <v>0.4088</v>
       </c>
       <c r="J152" t="n">
-        <v>12.288</v>
+        <v>12.264</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1765</v>
+        <v>0.1865</v>
       </c>
       <c r="J153" t="n">
-        <v>5.295</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1331</v>
+        <v>0.1435</v>
       </c>
       <c r="J154" t="n">
-        <v>3.993</v>
+        <v>4.305</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0236</v>
+        <v>-0.0275</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.708</v>
+        <v>-0.825</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1602</v>
+        <v>-0.1725</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.806</v>
+        <v>-5.175</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9726</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>29.178</v>
+        <v>27.081</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3103</v>
+        <v>0.3086</v>
       </c>
       <c r="J158" t="n">
-        <v>9.308999999999999</v>
+        <v>9.257999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2052</v>
+        <v>-0.2057</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.156</v>
+        <v>-6.171</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4145</v>
+        <v>-0.4001</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.435</v>
+        <v>-12.003</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4145</v>
+        <v>-0.4001</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.435</v>
+        <v>-12.003</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6864</v>
+        <v>0.6515</v>
       </c>
       <c r="J162" t="n">
-        <v>17.8464</v>
+        <v>16.939</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1442</v>
+        <v>-0.1601</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.7492</v>
+        <v>-4.1626</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.83</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1953</v>
+        <v>-0.2119</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.0778</v>
+        <v>-5.5094</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.72</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3035</v>
+        <v>-0.3184</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.891</v>
+        <v>-8.2784</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.387600000000001</v>
+        <v>-8.762</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2651</v>
+        <v>1.2413</v>
       </c>
       <c r="J167" t="n">
-        <v>32.8926</v>
+        <v>32.2738</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.49</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1054</v>
+        <v>1.0698</v>
       </c>
       <c r="J168" t="n">
-        <v>28.7404</v>
+        <v>27.8148</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5143</v>
+        <v>0.5085</v>
       </c>
       <c r="J169" t="n">
-        <v>13.3718</v>
+        <v>13.221</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.17</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4639</v>
+        <v>0.4632</v>
       </c>
       <c r="J170" t="n">
-        <v>12.0614</v>
+        <v>12.0432</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.09</v>
       </c>
       <c r="I171" t="n">
-        <v>0.2476</v>
+        <v>0.2655</v>
       </c>
       <c r="J171" t="n">
-        <v>6.4376</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.22</v>
+        <v>0.2181</v>
       </c>
       <c r="J172" t="n">
-        <v>5.72</v>
+        <v>5.6706</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0669</v>
+        <v>0.0644</v>
       </c>
       <c r="J173" t="n">
-        <v>1.7394</v>
+        <v>1.6744</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0885</v>
+        <v>-0.1027</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.301</v>
+        <v>-2.6702</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.8266</v>
+        <v>-6.2608</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.58</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4338</v>
+        <v>-0.4438</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2788</v>
+        <v>-11.5388</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0649</v>
+        <v>1.0209</v>
       </c>
       <c r="J177" t="n">
-        <v>27.6874</v>
+        <v>26.5434</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8689</v>
+        <v>0.8219</v>
       </c>
       <c r="J178" t="n">
-        <v>22.5914</v>
+        <v>21.3694</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.28</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7347</v>
+        <v>0.7036</v>
       </c>
       <c r="J179" t="n">
-        <v>19.1022</v>
+        <v>18.2936</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5745</v>
+        <v>0.5603</v>
       </c>
       <c r="J180" t="n">
-        <v>14.937</v>
+        <v>14.5678</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.01</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.008</v>
+        <v>0.0163</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.208</v>
+        <v>0.4238</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.95</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0304</v>
+        <v>1.0168</v>
       </c>
       <c r="J182" t="n">
-        <v>24.7296</v>
+        <v>24.4032</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.8</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9062</v>
+        <v>0.8909</v>
       </c>
       <c r="J183" t="n">
-        <v>21.7488</v>
+        <v>21.3816</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1772</v>
+        <v>0.1994</v>
       </c>
       <c r="J184" t="n">
-        <v>4.2528</v>
+        <v>4.7856</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0964</v>
+        <v>-0.0984</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.3136</v>
+        <v>-2.3616</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2004</v>
+        <v>-0.2065</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.8096</v>
+        <v>-4.956</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4144</v>
+        <v>0.3991</v>
       </c>
       <c r="J187" t="n">
-        <v>9.945600000000001</v>
+        <v>9.5784</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0189</v>
+        <v>0.0015</v>
       </c>
       <c r="J188" t="n">
-        <v>0.4536</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3552</v>
+        <v>-0.3711</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.524800000000001</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.58</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4208</v>
+        <v>-0.4336</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.0992</v>
+        <v>-10.4064</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.49</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5042</v>
+        <v>-0.5123</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.1008</v>
+        <v>-12.2952</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6583</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>23.0405</v>
+        <v>22.176</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4067</v>
+        <v>0.403</v>
       </c>
       <c r="J193" t="n">
-        <v>14.2345</v>
+        <v>14.105</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3689</v>
+        <v>0.3676</v>
       </c>
       <c r="J194" t="n">
-        <v>12.9115</v>
+        <v>12.866</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3154</v>
+        <v>-0.3277</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.039</v>
+        <v>-11.4695</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.482</v>
+        <v>-0.4878</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.87</v>
+        <v>-17.073</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0007</v>
+        <v>0.9413</v>
       </c>
       <c r="J197" t="n">
-        <v>35.0245</v>
+        <v>32.9455</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4696</v>
+        <v>0.4615</v>
       </c>
       <c r="J198" t="n">
-        <v>16.436</v>
+        <v>16.1525</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4696</v>
+        <v>0.4615</v>
       </c>
       <c r="J199" t="n">
-        <v>16.436</v>
+        <v>16.1525</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.07</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2255</v>
+        <v>0.236</v>
       </c>
       <c r="J200" t="n">
-        <v>7.8925</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0374</v>
+        <v>-0.0257</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.309</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.229</v>
+        <v>1.2073</v>
       </c>
       <c r="J202" t="n">
-        <v>27.038</v>
+        <v>26.5606</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.61</v>
       </c>
       <c r="I203" t="n">
-        <v>1.229</v>
+        <v>1.2073</v>
       </c>
       <c r="J203" t="n">
-        <v>27.038</v>
+        <v>26.5606</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9787</v>
+        <v>0.9304</v>
       </c>
       <c r="J204" t="n">
-        <v>21.5314</v>
+        <v>20.4688</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.9223</v>
+        <v>0.8758</v>
       </c>
       <c r="J205" t="n">
-        <v>20.2906</v>
+        <v>19.2676</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.21</v>
       </c>
       <c r="I206" t="n">
-        <v>0.5354</v>
+        <v>0.5331</v>
       </c>
       <c r="J206" t="n">
-        <v>11.7788</v>
+        <v>11.7282</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2315</v>
+        <v>0.2093</v>
       </c>
       <c r="J207" t="n">
-        <v>5.093</v>
+        <v>4.6046</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.77</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2332</v>
+        <v>-0.2543</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.1304</v>
+        <v>-5.5946</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.7</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2985</v>
+        <v>-0.3183</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.567</v>
+        <v>-7.0026</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.58</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4099</v>
+        <v>-0.4251</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.017799999999999</v>
+        <v>-9.3522</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5127</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.2794</v>
+        <v>-11.4774</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.91</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.914</v>
+        <v>-2.3672</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1557</v>
+        <v>-0.1767</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.4254</v>
+        <v>-3.8874</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.7</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3023</v>
+        <v>-0.3212</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.6506</v>
+        <v>-7.0664</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.63</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3679</v>
+        <v>-0.3843</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.0938</v>
+        <v>-8.454599999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3772</v>
+        <v>-0.3932</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.298400000000001</v>
+        <v>-8.650399999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.64</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7327</v>
+        <v>0.7328</v>
       </c>
       <c r="J217" t="n">
-        <v>16.1194</v>
+        <v>16.1216</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.58</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6763</v>
       </c>
       <c r="J218" t="n">
-        <v>14.7818</v>
+        <v>14.8786</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.49</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5799</v>
+        <v>0.59</v>
       </c>
       <c r="J219" t="n">
-        <v>12.7578</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.21</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2724</v>
+        <v>0.2949</v>
       </c>
       <c r="J220" t="n">
-        <v>5.9928</v>
+        <v>6.4878</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.196</v>
+        <v>0.2199</v>
       </c>
       <c r="J221" t="n">
-        <v>4.312</v>
+        <v>4.8378</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2021</v>
+        <v>1.1792</v>
       </c>
       <c r="J222" t="n">
-        <v>25.2441</v>
+        <v>24.7632</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0613</v>
+        <v>1.0236</v>
       </c>
       <c r="J223" t="n">
-        <v>22.2873</v>
+        <v>21.4956</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.46</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0493</v>
+        <v>1.0093</v>
       </c>
       <c r="J224" t="n">
-        <v>22.0353</v>
+        <v>21.1953</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0229</v>
+        <v>0.9785</v>
       </c>
       <c r="J225" t="n">
-        <v>21.4809</v>
+        <v>20.5485</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.38</v>
       </c>
       <c r="I226" t="n">
-        <v>0.9182</v>
+        <v>0.8729</v>
       </c>
       <c r="J226" t="n">
-        <v>19.2822</v>
+        <v>18.3309</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.86</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1122</v>
+        <v>-0.1402</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.3562</v>
+        <v>-2.9442</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.73</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2555</v>
+        <v>-0.2794</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.3655</v>
+        <v>-5.8674</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3425</v>
+        <v>-0.3631</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.1925</v>
+        <v>-7.6251</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.51</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4608</v>
+        <v>-0.4754</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.6768</v>
+        <v>-9.9834</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.4</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5649</v>
+        <v>-0.5722</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.8629</v>
+        <v>-12.0162</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1107</v>
+        <v>1.0694</v>
       </c>
       <c r="J232" t="n">
-        <v>28.8782</v>
+        <v>27.8044</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.42</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0443</v>
+        <v>0.9918</v>
       </c>
       <c r="J233" t="n">
-        <v>27.1518</v>
+        <v>25.7868</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5411</v>
+        <v>0.5268</v>
       </c>
       <c r="J234" t="n">
-        <v>14.0686</v>
+        <v>13.6968</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3661</v>
+        <v>-0.3475</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.518599999999999</v>
+        <v>-9.035</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5352</v>
+        <v>-0.5016</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.9152</v>
+        <v>-13.0416</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4045</v>
+        <v>0.3976</v>
       </c>
       <c r="J237" t="n">
-        <v>10.517</v>
+        <v>10.3376</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.13</v>
       </c>
       <c r="I238" t="n">
-        <v>0.326</v>
+        <v>0.3241</v>
       </c>
       <c r="J238" t="n">
-        <v>8.476000000000001</v>
+        <v>8.426600000000001</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1701</v>
+        <v>-0.1852</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.4226</v>
+        <v>-4.8152</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.201</v>
+        <v>-0.2163</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.226</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3382</v>
+        <v>-0.351</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.793200000000001</v>
+        <v>-9.125999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1787</v>
+        <v>1.1444</v>
       </c>
       <c r="J242" t="n">
-        <v>31.8249</v>
+        <v>30.8988</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.9061</v>
+        <v>0.8519</v>
       </c>
       <c r="J243" t="n">
-        <v>24.4647</v>
+        <v>23.0013</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3838</v>
+        <v>0.3852</v>
       </c>
       <c r="J244" t="n">
-        <v>10.3626</v>
+        <v>10.4004</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0835</v>
+        <v>0.1035</v>
       </c>
       <c r="J245" t="n">
-        <v>2.2545</v>
+        <v>2.7945</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.98</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1457</v>
+        <v>-0.1356</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.9339</v>
+        <v>-3.6612</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2503</v>
+        <v>0.2505</v>
       </c>
       <c r="J247" t="n">
-        <v>6.7581</v>
+        <v>6.7635</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2503</v>
+        <v>0.2505</v>
       </c>
       <c r="J248" t="n">
-        <v>6.7581</v>
+        <v>6.7635</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0927</v>
+        <v>-0.1059</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.5029</v>
+        <v>-2.8593</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2189</v>
+        <v>-0.2346</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.9103</v>
+        <v>-6.3342</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3641</v>
+        <v>-0.3763</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.8307</v>
+        <v>-10.1601</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.96</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0306</v>
+        <v>-0.0473</v>
       </c>
       <c r="J252" t="n">
-        <v>-0.6732</v>
+        <v>-1.0406</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.88</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.129</v>
+        <v>-0.1485</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.838</v>
+        <v>-3.267</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2597</v>
+        <v>-0.2787</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.7134</v>
+        <v>-6.1314</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2597</v>
+        <v>-0.2787</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.7134</v>
+        <v>-6.1314</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4661</v>
+        <v>-0.4766</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.2542</v>
+        <v>-10.4852</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.52</v>
       </c>
       <c r="I257" t="n">
-        <v>0.623</v>
+        <v>0.6283</v>
       </c>
       <c r="J257" t="n">
-        <v>13.706</v>
+        <v>13.8226</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.47</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5787</v>
       </c>
       <c r="J258" t="n">
-        <v>12.5422</v>
+        <v>12.7314</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.44</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5381</v>
+        <v>0.5486</v>
       </c>
       <c r="J259" t="n">
-        <v>11.8382</v>
+        <v>12.0692</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1929</v>
+        <v>0.2145</v>
       </c>
       <c r="J260" t="n">
-        <v>4.2438</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0453</v>
+        <v>0.0644</v>
       </c>
       <c r="J261" t="n">
-        <v>0.9966</v>
+        <v>1.4168</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.84</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5452</v>
+        <v>1.5345</v>
       </c>
       <c r="J262" t="n">
-        <v>44.8108</v>
+        <v>44.5005</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7129</v>
+        <v>0.6841</v>
       </c>
       <c r="J263" t="n">
-        <v>20.6741</v>
+        <v>19.8389</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.26</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6905</v>
+        <v>0.6641</v>
       </c>
       <c r="J264" t="n">
-        <v>20.0245</v>
+        <v>19.2589</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.1</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2898</v>
+        <v>0.3014</v>
       </c>
       <c r="J265" t="n">
-        <v>8.404199999999999</v>
+        <v>8.740600000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6875</v>
+        <v>-0.6341</v>
       </c>
       <c r="J266" t="n">
-        <v>-19.9375</v>
+        <v>-18.3889</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.47</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.8972</v>
       </c>
       <c r="J267" t="n">
-        <v>27.7588</v>
+        <v>26.0188</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1135</v>
+        <v>-0.1282</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.2915</v>
+        <v>-3.7178</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1658</v>
+        <v>-0.1819</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.8082</v>
+        <v>-5.2751</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3239</v>
+        <v>-0.338</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.3931</v>
+        <v>-9.802</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4637</v>
+        <v>-0.4719</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.4473</v>
+        <v>-13.6851</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.06</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8006</v>
+        <v>1.8009</v>
       </c>
       <c r="J272" t="n">
-        <v>45.015</v>
+        <v>45.0225</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.35</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8895</v>
+        <v>0.8403</v>
       </c>
       <c r="J273" t="n">
-        <v>22.2375</v>
+        <v>21.0075</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.12</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3431</v>
+        <v>0.351</v>
       </c>
       <c r="J274" t="n">
-        <v>8.577500000000001</v>
+        <v>8.775</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.02</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0317</v>
+        <v>0.0567</v>
       </c>
       <c r="J275" t="n">
-        <v>0.7925</v>
+        <v>1.4175</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.77</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.766</v>
+        <v>-0.7033</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.15</v>
+        <v>-17.5825</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="J277" t="n">
-        <v>9.289999999999999</v>
+        <v>9.1425</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.08</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2273</v>
+        <v>0.2287</v>
       </c>
       <c r="J278" t="n">
-        <v>5.6825</v>
+        <v>5.7175</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1472</v>
+        <v>-0.1624</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.68</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.205</v>
+        <v>-4.595</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3926</v>
+        <v>-0.4037</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.815</v>
+        <v>-10.0925</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.91</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5604</v>
+        <v>1.5611</v>
       </c>
       <c r="J282" t="n">
-        <v>29.6476</v>
+        <v>29.6609</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.69</v>
       </c>
       <c r="I283" t="n">
-        <v>1.3117</v>
+        <v>1.2978</v>
       </c>
       <c r="J283" t="n">
-        <v>24.9223</v>
+        <v>24.6582</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.61</v>
       </c>
       <c r="I284" t="n">
-        <v>1.2198</v>
+        <v>1.1994</v>
       </c>
       <c r="J284" t="n">
-        <v>23.1762</v>
+        <v>22.7886</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.41</v>
       </c>
       <c r="I285" t="n">
-        <v>0.969</v>
+        <v>0.9227</v>
       </c>
       <c r="J285" t="n">
-        <v>18.411</v>
+        <v>17.5313</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3498</v>
+        <v>-0.315</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.6462</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.92</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0475</v>
+        <v>-0.0737</v>
       </c>
       <c r="J287" t="n">
-        <v>-0.9025</v>
+        <v>-1.4003</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0604</v>
+        <v>-0.0866</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.1476</v>
+        <v>-1.6454</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3816</v>
+        <v>-0.3999</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.2504</v>
+        <v>-7.5981</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.54</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4374</v>
+        <v>-0.4527</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.310600000000001</v>
+        <v>-8.6013</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.3</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6636</v>
+        <v>-0.6625</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.6084</v>
+        <v>-12.5875</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.6304</v>
+        <v>1.6376</v>
       </c>
       <c r="J292" t="n">
-        <v>30.9776</v>
+        <v>31.1144</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.84</v>
       </c>
       <c r="I293" t="n">
-        <v>1.4662</v>
+        <v>1.4646</v>
       </c>
       <c r="J293" t="n">
-        <v>27.8578</v>
+        <v>27.8274</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.7</v>
       </c>
       <c r="I294" t="n">
-        <v>1.3109</v>
+        <v>1.2994</v>
       </c>
       <c r="J294" t="n">
-        <v>24.9071</v>
+        <v>24.6886</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>1.0349</v>
+        <v>0.996</v>
       </c>
       <c r="J295" t="n">
-        <v>19.6631</v>
+        <v>18.924</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0655</v>
+        <v>0.1086</v>
       </c>
       <c r="J296" t="n">
-        <v>1.2445</v>
+        <v>2.0634</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.73</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.2295</v>
+        <v>-0.2591</v>
       </c>
       <c r="J297" t="n">
-        <v>-4.3605</v>
+        <v>-4.9229</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.64</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3249</v>
+        <v>-0.3495</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.1731</v>
+        <v>-6.6405</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.335</v>
+        <v>-0.359</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.365</v>
+        <v>-6.821</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5692</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.8148</v>
+        <v>-10.9839</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5887</v>
+        <v>-0.596</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.1853</v>
+        <v>-11.324</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.41</v>
       </c>
       <c r="I302" t="n">
-        <v>1.0302</v>
+        <v>0.975</v>
       </c>
       <c r="J302" t="n">
-        <v>36.057</v>
+        <v>34.125</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.39</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9977</v>
+        <v>0.9387</v>
       </c>
       <c r="J303" t="n">
-        <v>34.9195</v>
+        <v>32.8545</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.2</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5658</v>
+        <v>0.549</v>
       </c>
       <c r="J304" t="n">
-        <v>19.803</v>
+        <v>19.215</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1733</v>
+        <v>-0.1654</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.0655</v>
+        <v>-5.789</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5074</v>
+        <v>-0.4767</v>
       </c>
       <c r="J306" t="n">
-        <v>-17.759</v>
+        <v>-16.6845</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.51</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9807</v>
+        <v>0.9266</v>
       </c>
       <c r="J307" t="n">
-        <v>34.3245</v>
+        <v>32.431</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.99</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.018</v>
+        <v>-0.0233</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.63</v>
+        <v>-0.8155</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.92</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1079</v>
+        <v>-0.1207</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.7765</v>
+        <v>-4.2245</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.8</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2348</v>
+        <v>-0.2491</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.218</v>
+        <v>-8.718500000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4254</v>
+        <v>-0.4342</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.889</v>
+        <v>-15.197</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.38</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9796</v>
+        <v>0.9197</v>
       </c>
       <c r="J312" t="n">
-        <v>27.4288</v>
+        <v>25.7516</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7097</v>
+        <v>0.6772</v>
       </c>
       <c r="J313" t="n">
-        <v>19.8716</v>
+        <v>18.9616</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.25</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6859</v>
+        <v>0.6562</v>
       </c>
       <c r="J314" t="n">
-        <v>19.2052</v>
+        <v>18.3736</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3103</v>
+        <v>0.3156</v>
       </c>
       <c r="J315" t="n">
-        <v>8.6884</v>
+        <v>8.8368</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5616</v>
+        <v>-0.5255</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.7248</v>
+        <v>-14.714</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4957</v>
+        <v>0.4826</v>
       </c>
       <c r="J317" t="n">
-        <v>13.8796</v>
+        <v>13.5128</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3823</v>
+        <v>0.3775</v>
       </c>
       <c r="J318" t="n">
-        <v>10.7044</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1059</v>
+        <v>-0.1192</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.9652</v>
+        <v>-3.3376</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2223</v>
+        <v>-0.2372</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.2244</v>
+        <v>-6.6416</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.414</v>
+        <v>-0.4236</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.592</v>
+        <v>-11.8608</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3714/event_3714_evp_summary.xlsx
+++ b/database/event/3714/event_3714_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.99</v>
+        <v>5.9883</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9328</v>
+        <v>0.9325</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1026</v>
+        <v>2.1222</v>
       </c>
       <c r="E2" t="n">
-        <v>5.99</v>
+        <v>5.9883</v>
       </c>
       <c r="F2" t="n">
-        <v>2.946</v>
+        <v>2.968</v>
       </c>
       <c r="G2" t="n">
-        <v>3.044</v>
+        <v>3.0203</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8258</v>
+        <v>4.7007</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6059</v>
+        <v>2.6393</v>
       </c>
       <c r="J2" t="n">
-        <v>3.044</v>
+        <v>3.0203</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>114</v>
       </c>
       <c r="M2" t="n">
-        <v>5.649900000000001</v>
+        <v>5.6596</v>
       </c>
       <c r="N2" t="n">
         <v>255</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7807</v>
+        <v>5.6691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9002</v>
+        <v>0.8828</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0073</v>
+        <v>1.9768</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7807</v>
+        <v>5.6691</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7312</v>
+        <v>2.6496</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0495</v>
+        <v>3.0195</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2529</v>
+        <v>3.122</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2529</v>
+        <v>3.122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0495</v>
+        <v>3.0195</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>6.3024</v>
+        <v>6.1415</v>
       </c>
       <c r="N3" t="n">
         <v>254</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8647</v>
+        <v>4.8887</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7613</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5903</v>
+        <v>1.6212</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8647</v>
+        <v>4.8887</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6491</v>
+        <v>3.554</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2156</v>
+        <v>1.3347</v>
       </c>
       <c r="H4" t="n">
-        <v>7.1455</v>
+        <v>6.9005</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8585</v>
+        <v>3.8744</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2156</v>
+        <v>1.3347</v>
       </c>
       <c r="K4" t="n">
         <v>139</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0741</v>
+        <v>5.2091</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6199</v>
+        <v>4.4317</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7194</v>
+        <v>0.6901</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4789</v>
+        <v>1.4131</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6199</v>
+        <v>4.4317</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9724</v>
+        <v>1.8592</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6475</v>
+        <v>2.5725</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9724</v>
+        <v>1.8592</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0651</v>
+        <v>1.0439</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6475</v>
+        <v>2.5725</v>
       </c>
       <c r="K5" t="n">
         <v>139</v>
@@ -667,7 +667,7 @@
         <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7126</v>
+        <v>3.6164</v>
       </c>
       <c r="N5" t="n">
         <v>256</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2811</v>
+        <v>4.0867</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6667</v>
+        <v>0.6364</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3246</v>
+        <v>1.2559</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2811</v>
+        <v>4.0867</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2057</v>
+        <v>3.1033</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0754</v>
+        <v>0.9835</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2913</v>
+        <v>4.1617</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4019</v>
+        <v>4.2729</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0754</v>
+        <v>0.9835</v>
       </c>
       <c r="K6" t="n">
         <v>114</v>
@@ -713,7 +713,7 @@
         <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>5.477300000000001</v>
+        <v>5.2564</v>
       </c>
       <c r="N6" t="n">
         <v>190</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0916</v>
+        <v>3.9746</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6372</v>
+        <v>0.6189</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2384</v>
+        <v>1.2048</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0916</v>
+        <v>3.9746</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5551</v>
+        <v>3.4614</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5365</v>
+        <v>0.5132</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8353</v>
+        <v>6.553</v>
       </c>
       <c r="I7" t="n">
-        <v>3.691</v>
+        <v>3.6793</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5365</v>
+        <v>0.5132</v>
       </c>
       <c r="K7" t="n">
         <v>139</v>
@@ -759,7 +759,7 @@
         <v>117</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2275</v>
+        <v>4.1925</v>
       </c>
       <c r="N7" t="n">
         <v>256</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6576</v>
+        <v>3.5601</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5696</v>
+        <v>0.5544</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0408</v>
+        <v>1.016</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6576</v>
+        <v>3.5601</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6837</v>
+        <v>2.6754</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9739</v>
+        <v>0.8847</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1489</v>
+        <v>3.1811</v>
       </c>
       <c r="I8" t="n">
-        <v>3.23</v>
+        <v>3.2661</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9739</v>
+        <v>0.8847</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2039</v>
+        <v>4.1508</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.086</v>
+        <v>3.1668</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4806</v>
+        <v>0.4931</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7806</v>
+        <v>0.8368</v>
       </c>
       <c r="E9" t="n">
-        <v>3.086</v>
+        <v>3.1668</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9739</v>
+        <v>2.0301</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1121</v>
+        <v>1.1367</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9739</v>
+        <v>2.0301</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9739</v>
+        <v>2.0301</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1121</v>
+        <v>1.1367</v>
       </c>
       <c r="K9" t="n">
         <v>116</v>
@@ -851,7 +851,7 @@
         <v>138</v>
       </c>
       <c r="M9" t="n">
-        <v>3.086</v>
+        <v>3.1668</v>
       </c>
       <c r="N9" t="n">
         <v>254</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.915</v>
+        <v>2.8091</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4539</v>
+        <v>0.4374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7028</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.915</v>
+        <v>2.8091</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6485</v>
+        <v>1.6705</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2665</v>
+        <v>1.1386</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6485</v>
+        <v>1.6705</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6485</v>
+        <v>1.6705</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2665</v>
+        <v>1.1386</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>2.915</v>
+        <v>2.8091</v>
       </c>
       <c r="N10" t="n">
         <v>203</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.847</v>
+        <v>2.6466</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4433</v>
+        <v>0.4121</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6718</v>
+        <v>0.5999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.847</v>
+        <v>2.6466</v>
       </c>
       <c r="F11" t="n">
-        <v>1.736</v>
+        <v>3.1654</v>
       </c>
       <c r="G11" t="n">
-        <v>1.111</v>
+        <v>-0.5188</v>
       </c>
       <c r="H11" t="n">
-        <v>1.736</v>
+        <v>5.4416</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9374</v>
+        <v>3.0553</v>
       </c>
       <c r="J11" t="n">
-        <v>1.111</v>
+        <v>-0.5188</v>
       </c>
       <c r="K11" t="n">
         <v>141</v>
@@ -943,7 +943,7 @@
         <v>114</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0484</v>
+        <v>2.5365</v>
       </c>
       <c r="N11" t="n">
         <v>255</v>
@@ -952,127 +952,127 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8416</v>
+        <v>2.6397</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4425</v>
+        <v>0.4111</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6694</v>
+        <v>0.5967</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8416</v>
+        <v>2.6397</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1314</v>
+        <v>-0.8663</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7102000000000001</v>
+        <v>3.506</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1314</v>
+        <v>-0.8663</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1863</v>
+        <v>-0.4864</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7102000000000001</v>
+        <v>3.506</v>
       </c>
       <c r="K12" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="L12" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8965</v>
+        <v>3.0196</v>
       </c>
       <c r="N12" t="n">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7349</v>
+        <v>2.5974</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4259</v>
+        <v>0.4045</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6208</v>
+        <v>0.5775</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7349</v>
+        <v>2.5974</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2143</v>
+        <v>1.9242</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4794</v>
+        <v>0.6732</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7108</v>
+        <v>1.9242</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0838</v>
+        <v>1.9756</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4794</v>
+        <v>0.6732</v>
       </c>
       <c r="K13" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6044</v>
+        <v>2.6488</v>
       </c>
       <c r="N13" t="n">
-        <v>255</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6744</v>
+        <v>2.5331</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4165</v>
+        <v>0.3945</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5482</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6744</v>
+        <v>2.5331</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4224</v>
+        <v>1.5043</v>
       </c>
       <c r="G14" t="n">
-        <v>2.252</v>
+        <v>1.0288</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4224</v>
+        <v>1.5043</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2281</v>
+        <v>0.8446</v>
       </c>
       <c r="J14" t="n">
-        <v>2.252</v>
+        <v>1.0288</v>
       </c>
       <c r="K14" t="n">
         <v>141</v>
@@ -1081,7 +1081,7 @@
         <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4801</v>
+        <v>1.8734</v>
       </c>
       <c r="N14" t="n">
         <v>255</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6047</v>
+        <v>2.4828</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4056</v>
+        <v>0.3866</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5615</v>
+        <v>0.5252</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6047</v>
+        <v>2.4828</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1455</v>
+        <v>0.3332</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4592</v>
+        <v>2.1496</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1847</v>
+        <v>0.3332</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1797</v>
+        <v>0.1871</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4592</v>
+        <v>2.1496</v>
       </c>
       <c r="K15" t="n">
         <v>141</v>
@@ -1127,7 +1127,7 @@
         <v>114</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6389</v>
+        <v>2.3367</v>
       </c>
       <c r="N15" t="n">
         <v>255</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5302</v>
+        <v>2.4691</v>
       </c>
       <c r="C16" t="n">
-        <v>0.394</v>
+        <v>0.3845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5276</v>
+        <v>0.519</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5302</v>
+        <v>2.4691</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9117</v>
+        <v>2.0429</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4419</v>
+        <v>0.4262</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9117</v>
+        <v>2.0429</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4923</v>
+        <v>1.147</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4419</v>
+        <v>0.4262</v>
       </c>
       <c r="K16" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L16" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9496</v>
+        <v>1.5732</v>
       </c>
       <c r="N16" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.432</v>
+        <v>2.466</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3787</v>
+        <v>0.384</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4829</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.432</v>
+        <v>2.466</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9555</v>
+        <v>2.0024</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4765</v>
+        <v>0.4636</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9555</v>
+        <v>2.0024</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0059</v>
+        <v>2.0559</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4765</v>
+        <v>0.4636</v>
       </c>
       <c r="K17" t="n">
         <v>114</v>
@@ -1219,7 +1219,7 @@
         <v>76</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4824</v>
+        <v>2.5195</v>
       </c>
       <c r="N17" t="n">
         <v>190</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9845</v>
+        <v>1.9554</v>
       </c>
       <c r="C18" t="n">
-        <v>0.309</v>
+        <v>0.3045</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2792</v>
+        <v>0.285</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9845</v>
+        <v>1.9554</v>
       </c>
       <c r="F18" t="n">
-        <v>2.322</v>
+        <v>2.312</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3375</v>
+        <v>-0.3566</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3573</v>
+        <v>2.3483</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3573</v>
+        <v>2.3483</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3375</v>
+        <v>-0.3566</v>
       </c>
       <c r="K18" t="n">
         <v>121</v>
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0198</v>
+        <v>1.9917</v>
       </c>
       <c r="N18" t="n">
         <v>203</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8884</v>
+        <v>1.805</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2941</v>
+        <v>0.2811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2354</v>
+        <v>0.2165</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8884</v>
+        <v>1.805</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8635</v>
+        <v>1.7817</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0249</v>
+        <v>0.0233</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8635</v>
+        <v>1.7817</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9115</v>
+        <v>1.8293</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0249</v>
+        <v>0.0233</v>
       </c>
       <c r="K19" t="n">
         <v>145</v>
@@ -1311,7 +1311,7 @@
         <v>129</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9364</v>
+        <v>1.8526</v>
       </c>
       <c r="N19" t="n">
         <v>274</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8033</v>
+        <v>1.6481</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2808</v>
+        <v>0.2567</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1967</v>
+        <v>0.145</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8033</v>
+        <v>1.6481</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3873</v>
+        <v>1.3405</v>
       </c>
       <c r="G20" t="n">
-        <v>0.416</v>
+        <v>0.3076</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3873</v>
+        <v>1.3405</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3873</v>
+        <v>1.3405</v>
       </c>
       <c r="J20" t="n">
-        <v>0.416</v>
+        <v>0.3076</v>
       </c>
       <c r="K20" t="n">
         <v>121</v>
@@ -1357,7 +1357,7 @@
         <v>82</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8033</v>
+        <v>1.6481</v>
       </c>
       <c r="N20" t="n">
         <v>203</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2705</v>
+        <v>1.3475</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1978</v>
+        <v>0.2098</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0458</v>
+        <v>0.0081</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2705</v>
+        <v>1.3475</v>
       </c>
       <c r="F21" t="n">
-        <v>1.873</v>
+        <v>1.8927</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6025</v>
+        <v>-0.5452</v>
       </c>
       <c r="H21" t="n">
-        <v>1.873</v>
+        <v>1.8927</v>
       </c>
       <c r="I21" t="n">
-        <v>1.873</v>
+        <v>1.8927</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6025</v>
+        <v>-0.5452</v>
       </c>
       <c r="K21" t="n">
         <v>121</v>
@@ -1403,7 +1403,7 @@
         <v>82</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2705</v>
+        <v>1.3475</v>
       </c>
       <c r="N21" t="n">
         <v>203</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2618</v>
+        <v>1.1351</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1965</v>
+        <v>0.1768</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0498</v>
+        <v>-0.0887</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2618</v>
+        <v>1.1351</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4729</v>
+        <v>0.3832</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7889</v>
+        <v>0.7519</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4729</v>
+        <v>0.3832</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4851</v>
+        <v>0.3935</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7889</v>
+        <v>0.7519</v>
       </c>
       <c r="K22" t="n">
         <v>145</v>
@@ -1449,7 +1449,7 @@
         <v>129</v>
       </c>
       <c r="M22" t="n">
-        <v>1.274</v>
+        <v>1.1454</v>
       </c>
       <c r="N22" t="n">
         <v>274</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1116</v>
+        <v>1.0581</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1731</v>
+        <v>0.1648</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1182</v>
+        <v>-0.1238</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1116</v>
+        <v>1.0581</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7664</v>
+        <v>1.3596</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3452</v>
+        <v>-0.3015</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7664</v>
+        <v>1.3596</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7862</v>
+        <v>1.3596</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3452</v>
+        <v>-0.3015</v>
       </c>
       <c r="K23" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="L23" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1314</v>
+        <v>1.0581</v>
       </c>
       <c r="N23" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0391</v>
+        <v>1.013</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1618</v>
+        <v>0.1577</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1512</v>
+        <v>-0.1443</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0391</v>
+        <v>1.013</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3312</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2921</v>
+        <v>0.2757</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3312</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3312</v>
+        <v>0.7571</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2921</v>
+        <v>0.2757</v>
       </c>
       <c r="K24" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="L24" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0391</v>
+        <v>1.0328</v>
       </c>
       <c r="N24" t="n">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0094</v>
+        <v>0.9695</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1572</v>
+        <v>0.151</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1647</v>
+        <v>-0.1641</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0094</v>
+        <v>0.9695</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3691</v>
+        <v>1.3122</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3597</v>
+        <v>-0.3427</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3691</v>
+        <v>1.3122</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4044</v>
+        <v>1.3472</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3597</v>
+        <v>-0.3427</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0447</v>
+        <v>1.0045</v>
       </c>
       <c r="N25" t="n">
         <v>190</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1318</v>
+        <v>0.1117</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.239</v>
+        <v>-0.2791</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0916</v>
+        <v>0.065</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3563</v>
+        <v>-0.4156</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5885</v>
+        <v>0.4175</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3849</v>
+        <v>0.363</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0599</v>
+        <v>0.0565</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.449</v>
+        <v>-0.4404</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3849</v>
+        <v>0.363</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7454</v>
+        <v>0.6856</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3605</v>
+        <v>-0.3226</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7454</v>
+        <v>0.6856</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7454</v>
+        <v>0.6856</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3605</v>
+        <v>-0.3226</v>
       </c>
       <c r="K28" t="n">
         <v>116</v>
@@ -1725,7 +1725,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3849</v>
+        <v>0.363</v>
       </c>
       <c r="N28" t="n">
         <v>254</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="C29" t="n">
-        <v>0.005</v>
+        <v>-0.0101</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6095</v>
+        <v>-0.6354</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0324</v>
+        <v>-0.065</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0231</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6532</v>
+        <v>-0.6733</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1483</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0179</v>
+        <v>-0.03</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6765</v>
+        <v>-0.6936</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1149</v>
+        <v>-0.1927</v>
       </c>
       <c r="N31" t="n">
         <v>125</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3646</v>
+        <v>-0.2467</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0568</v>
+        <v>-0.0384</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7902</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3646</v>
+        <v>-0.2467</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4823</v>
+        <v>-0.4406</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1177</v>
+        <v>0.1939</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4823</v>
+        <v>-0.4406</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4947</v>
+        <v>-0.4524</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1177</v>
+        <v>0.1939</v>
       </c>
       <c r="K32" t="n">
         <v>145</v>
@@ -1909,7 +1909,7 @@
         <v>129</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.377</v>
+        <v>-0.2585000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>274</v>
@@ -1918,231 +1918,231 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4019</v>
+        <v>-0.398</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0626</v>
+        <v>-0.062</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8072</v>
+        <v>-0.7871</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4019</v>
+        <v>-0.398</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4019</v>
+        <v>-1.0166</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.6186</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4019</v>
+        <v>-1.0166</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4019</v>
+        <v>-0.5708</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.6186</v>
       </c>
       <c r="K33" t="n">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4019</v>
+        <v>0.04780000000000006</v>
       </c>
       <c r="N33" t="n">
-        <v>91</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>xeta</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0668</v>
+        <v>-0.0626</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8196</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4292</v>
+        <v>-0.4017</v>
       </c>
       <c r="N34" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>xeta</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4325</v>
+        <v>-0.4085</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0674</v>
+        <v>-0.0636</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.7919</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4325</v>
+        <v>-0.4085</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0976</v>
+        <v>-0.4085</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6651</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0976</v>
+        <v>-0.4085</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5927</v>
+        <v>-0.4085</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6651</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="L35" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07240000000000002</v>
+        <v>-0.4085</v>
       </c>
       <c r="N35" t="n">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5623</v>
+        <v>-0.5639</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0876</v>
+        <v>-0.0878</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8802</v>
+        <v>-0.8627</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5623</v>
+        <v>-0.5639</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5623</v>
+        <v>-0.4012</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.1627</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5623</v>
+        <v>-0.4012</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5623</v>
+        <v>-0.4012</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.1627</v>
       </c>
       <c r="K36" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5623</v>
+        <v>-0.5639000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6469</v>
+        <v>-0.5836</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1007</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9187</v>
+        <v>-0.8716</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6469</v>
+        <v>-0.5836</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4486</v>
+        <v>-0.5836</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1983</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4486</v>
+        <v>-0.5836</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4486</v>
+        <v>-0.5836</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1983</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="L37" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6469</v>
+        <v>-0.5836</v>
       </c>
       <c r="N37" t="n">
-        <v>254</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.861</v>
+        <v>-0.8209</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1341</v>
+        <v>-0.1278</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0161</v>
+        <v>-0.9797</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.861</v>
+        <v>-0.8209</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2559</v>
+        <v>-1.2209</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3949</v>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2559</v>
+        <v>-1.2209</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2559</v>
+        <v>-1.2209</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3949</v>
+        <v>0.4</v>
       </c>
       <c r="K38" t="n">
         <v>116</v>
@@ -2185,7 +2185,7 @@
         <v>138</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.861</v>
+        <v>-0.8209000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>254</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1635</v>
+        <v>-0.1553</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1022</v>
+        <v>-1.06</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.05</v>
+        <v>-0.9971</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.269</v>
+        <v>-0.2646</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4105</v>
+        <v>-1.3799</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7273</v>
+        <v>-1.6992</v>
       </c>
       <c r="N40" t="n">
         <v>91</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3559</v>
+        <v>-2.3148</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3669</v>
+        <v>-0.3605</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6967</v>
+        <v>-1.6603</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3559</v>
+        <v>-2.3148</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2244</v>
+        <v>-1.2004</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.1315</v>
+        <v>-1.1144</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2244</v>
+        <v>-1.2004</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.256</v>
+        <v>-1.2325</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1315</v>
+        <v>-1.1144</v>
       </c>
       <c r="K41" t="n">
         <v>145</v>
@@ -2323,7 +2323,7 @@
         <v>129</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3875</v>
+        <v>-2.3469</v>
       </c>
       <c r="N41" t="n">
         <v>274</v>
@@ -2429,10 +2429,10 @@
         <v>1.87</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9246</v>
+        <v>0.8563</v>
       </c>
       <c r="J2" t="n">
-        <v>17.5674</v>
+        <v>16.2697</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.6338</v>
       </c>
       <c r="J3" t="n">
-        <v>13.3399</v>
+        <v>12.0422</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5274</v>
       </c>
       <c r="J4" t="n">
-        <v>11.2518</v>
+        <v>10.0206</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.49</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5826</v>
+        <v>0.5182</v>
       </c>
       <c r="J5" t="n">
-        <v>11.0694</v>
+        <v>9.845800000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3542</v>
+        <v>0.3013</v>
       </c>
       <c r="J6" t="n">
-        <v>6.7298</v>
+        <v>5.7247</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3505</v>
+        <v>0.3799</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6595</v>
+        <v>7.2181</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1632</v>
+        <v>-0.1453</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.1008</v>
+        <v>-2.7607</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.48</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5018</v>
+        <v>-0.5001</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.5342</v>
+        <v>-9.501899999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.38</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5897</v>
+        <v>-0.5998</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.2043</v>
+        <v>-11.3962</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.32</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6423</v>
+        <v>-0.6614</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.2037</v>
+        <v>-12.5666</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1979</v>
+        <v>0.1685</v>
       </c>
       <c r="J12" t="n">
-        <v>3.958</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.93</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.081</v>
+        <v>-0.0667</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.62</v>
+        <v>-1.334</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2937</v>
+        <v>-0.2784</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.874</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.437</v>
+        <v>-0.4287</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.74</v>
+        <v>-8.574</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5764</v>
+        <v>-0.5858</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.528</v>
+        <v>-11.716</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6488</v>
+        <v>1.6774</v>
       </c>
       <c r="J17" t="n">
-        <v>32.976</v>
+        <v>33.548</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3584</v>
+        <v>1.3949</v>
       </c>
       <c r="J18" t="n">
-        <v>27.168</v>
+        <v>27.898</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7629</v>
       </c>
       <c r="J19" t="n">
-        <v>15.534</v>
+        <v>15.258</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6358</v>
+        <v>0.6133</v>
       </c>
       <c r="J20" t="n">
-        <v>12.716</v>
+        <v>12.266</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6149</v>
+        <v>0.5913</v>
       </c>
       <c r="J21" t="n">
-        <v>12.298</v>
+        <v>11.826</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6637</v>
+        <v>0.6117</v>
       </c>
       <c r="J22" t="n">
-        <v>14.6014</v>
+        <v>13.4574</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1393</v>
+        <v>-0.1218</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0646</v>
+        <v>-2.6796</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.88</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1608</v>
+        <v>-0.1423</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5376</v>
+        <v>-3.1306</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.72</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3194</v>
+        <v>-0.3023</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.0268</v>
+        <v>-6.6506</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3655</v>
+        <v>-0.3514</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.041</v>
+        <v>-7.7308</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6579</v>
+        <v>1.6911</v>
       </c>
       <c r="J27" t="n">
-        <v>36.4738</v>
+        <v>37.2042</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7486</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>16.4692</v>
+        <v>15.8906</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4301</v>
+        <v>0.3964</v>
       </c>
       <c r="J29" t="n">
-        <v>9.462199999999999</v>
+        <v>8.720800000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.272</v>
+        <v>-0.2341</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.984</v>
+        <v>-5.1502</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3573</v>
+        <v>-0.3171</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.8606</v>
+        <v>-6.9762</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8149</v>
+        <v>0.7988</v>
       </c>
       <c r="J32" t="n">
-        <v>23.6321</v>
+        <v>23.1652</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="J33" t="n">
-        <v>15.6542</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4375</v>
+        <v>0.4028</v>
       </c>
       <c r="J34" t="n">
-        <v>12.6875</v>
+        <v>11.6812</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2101</v>
+        <v>0.1806</v>
       </c>
       <c r="J35" t="n">
-        <v>6.0929</v>
+        <v>5.2374</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4212</v>
+        <v>-0.3789</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.2148</v>
+        <v>-10.9881</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2649</v>
+        <v>0.217</v>
       </c>
       <c r="J37" t="n">
-        <v>7.6821</v>
+        <v>6.293</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0823</v>
+        <v>0.0586</v>
       </c>
       <c r="J38" t="n">
-        <v>2.3867</v>
+        <v>1.6994</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0516</v>
+        <v>0.0347</v>
       </c>
       <c r="J39" t="n">
-        <v>1.4964</v>
+        <v>1.0063</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1531</v>
+        <v>-0.134</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.4399</v>
+        <v>-3.886</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3605</v>
+        <v>-0.3462</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.4545</v>
+        <v>-10.0398</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7734</v>
+        <v>0.7573</v>
       </c>
       <c r="J42" t="n">
-        <v>20.8818</v>
+        <v>20.4471</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7136</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>19.2672</v>
+        <v>18.8487</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2409</v>
+        <v>0.2091</v>
       </c>
       <c r="J44" t="n">
-        <v>6.5043</v>
+        <v>5.6457</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1581</v>
+        <v>-0.1267</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.2687</v>
+        <v>-3.4209</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3397</v>
+        <v>-0.2978</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.171900000000001</v>
+        <v>-8.0406</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6024</v>
       </c>
       <c r="J47" t="n">
-        <v>16.9965</v>
+        <v>16.2648</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0949</v>
+        <v>-0.0796</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.5623</v>
+        <v>-2.1492</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1416</v>
+        <v>-0.1231</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.8232</v>
+        <v>-3.3237</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2949</v>
+        <v>-0.2766</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.9623</v>
+        <v>-7.4682</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3044</v>
+        <v>-0.2865</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.2188</v>
+        <v>-7.7355</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3827</v>
+        <v>1.3934</v>
       </c>
       <c r="J52" t="n">
-        <v>40.0983</v>
+        <v>40.4086</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0764</v>
+        <v>1.0665</v>
       </c>
       <c r="J53" t="n">
-        <v>31.2156</v>
+        <v>30.9285</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.245</v>
+        <v>0.2148</v>
       </c>
       <c r="J54" t="n">
-        <v>7.105</v>
+        <v>6.2292</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3091</v>
+        <v>-0.2711</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.963900000000001</v>
+        <v>-7.8619</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3919</v>
+        <v>-0.3527</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.3651</v>
+        <v>-10.2283</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0.249</v>
+        <v>0.2026</v>
       </c>
       <c r="J57" t="n">
-        <v>7.221</v>
+        <v>5.8754</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2282</v>
+        <v>0.1838</v>
       </c>
       <c r="J58" t="n">
-        <v>6.6178</v>
+        <v>5.3302</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0106</v>
+        <v>0.0068</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3074</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2048</v>
+        <v>-0.1847</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.9392</v>
+        <v>-5.3563</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4304</v>
+        <v>-0.4226</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.4816</v>
+        <v>-12.2554</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.55</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0061</v>
+        <v>0.994</v>
       </c>
       <c r="J62" t="n">
-        <v>24.1464</v>
+        <v>23.856</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.45</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8716</v>
+        <v>0.8576</v>
       </c>
       <c r="J63" t="n">
-        <v>20.9184</v>
+        <v>20.5824</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7478</v>
       </c>
       <c r="J64" t="n">
-        <v>18.2544</v>
+        <v>17.9472</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3713</v>
+        <v>0.3391</v>
       </c>
       <c r="J65" t="n">
-        <v>8.911199999999999</v>
+        <v>8.138400000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.96</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.221</v>
+        <v>-0.1882</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.304</v>
+        <v>-4.5168</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1266</v>
+        <v>0.1022</v>
       </c>
       <c r="J67" t="n">
-        <v>3.0384</v>
+        <v>2.4528</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1257</v>
+        <v>-0.1107</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.0168</v>
+        <v>-2.6568</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3432</v>
+        <v>-0.3281</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.236800000000001</v>
+        <v>-7.8744</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3613</v>
+        <v>-0.3472</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.671200000000001</v>
+        <v>-8.332800000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3973</v>
+        <v>-0.3856</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.5352</v>
+        <v>-9.2544</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7462</v>
+        <v>0.7311</v>
       </c>
       <c r="J72" t="n">
-        <v>18.655</v>
+        <v>18.2775</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.29</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6572</v>
+        <v>0.6445</v>
       </c>
       <c r="J73" t="n">
-        <v>16.43</v>
+        <v>16.1125</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.2</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5179</v>
+        <v>0.5079</v>
       </c>
       <c r="J74" t="n">
-        <v>12.9475</v>
+        <v>12.6975</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3624</v>
+        <v>0.3283</v>
       </c>
       <c r="J75" t="n">
-        <v>9.06</v>
+        <v>8.2075</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0322</v>
+        <v>-0.0266</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.805</v>
+        <v>-0.665</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.5</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8026</v>
+        <v>0.7733</v>
       </c>
       <c r="J77" t="n">
-        <v>20.065</v>
+        <v>19.3325</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1406</v>
+        <v>-0.1225</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.515</v>
+        <v>-3.0625</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2351</v>
+        <v>-0.2151</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.8775</v>
+        <v>-5.3775</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2351</v>
+        <v>-0.2151</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.8775</v>
+        <v>-5.3775</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.59</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4392</v>
+        <v>-0.4323</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.98</v>
+        <v>-10.8075</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7861</v>
+        <v>0.844</v>
       </c>
       <c r="J82" t="n">
-        <v>22.0108</v>
+        <v>23.632</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5326</v>
+        <v>0.5628</v>
       </c>
       <c r="J83" t="n">
-        <v>14.9128</v>
+        <v>15.7584</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.87</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1842</v>
+        <v>-0.1636</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.1576</v>
+        <v>-4.5808</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.65</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3968</v>
+        <v>-0.3868</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.1104</v>
+        <v>-10.8304</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4233</v>
+        <v>-0.4161</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.8524</v>
+        <v>-11.6508</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.409</v>
+        <v>0.3458</v>
       </c>
       <c r="J87" t="n">
-        <v>11.452</v>
+        <v>9.682399999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2917</v>
+        <v>0.2384</v>
       </c>
       <c r="J88" t="n">
-        <v>8.1676</v>
+        <v>6.6752</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2794</v>
+        <v>0.2274</v>
       </c>
       <c r="J89" t="n">
-        <v>7.8232</v>
+        <v>6.3672</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2418</v>
+        <v>0.1944</v>
       </c>
       <c r="J90" t="n">
-        <v>6.7704</v>
+        <v>5.4432</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1917</v>
+        <v>-0.1715</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.3676</v>
+        <v>-4.802</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.68</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1963</v>
+        <v>1.1939</v>
       </c>
       <c r="J92" t="n">
-        <v>34.6927</v>
+        <v>34.6231</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7147</v>
+        <v>0.7005</v>
       </c>
       <c r="J93" t="n">
-        <v>20.7263</v>
+        <v>20.3145</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.335</v>
+        <v>0.3018</v>
       </c>
       <c r="J94" t="n">
-        <v>9.715</v>
+        <v>8.7522</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.96</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2064</v>
+        <v>-0.1721</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.9856</v>
+        <v>-4.9909</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2383</v>
+        <v>-0.2018</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.9107</v>
+        <v>-5.8522</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4462</v>
+        <v>0.3962</v>
       </c>
       <c r="J97" t="n">
-        <v>12.9398</v>
+        <v>11.4898</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1722</v>
+        <v>0.1348</v>
       </c>
       <c r="J98" t="n">
-        <v>4.9938</v>
+        <v>3.9092</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2702</v>
+        <v>-0.2512</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.8358</v>
+        <v>-7.2848</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.74</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2988</v>
+        <v>-0.2808</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.6652</v>
+        <v>-8.1432</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3818</v>
+        <v>-0.3689</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.0722</v>
+        <v>-10.6981</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4469</v>
+        <v>0.3936</v>
       </c>
       <c r="J102" t="n">
-        <v>13.407</v>
+        <v>11.808</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="J103" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0722</v>
+        <v>-0.058</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.166</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.91</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1351</v>
+        <v>-0.116</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.053</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1466</v>
+        <v>-0.127</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.398</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.45</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9031</v>
+        <v>0.8883</v>
       </c>
       <c r="J107" t="n">
-        <v>27.093</v>
+        <v>26.649</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6825</v>
+        <v>0.6677</v>
       </c>
       <c r="J108" t="n">
-        <v>20.475</v>
+        <v>20.031</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3947</v>
+        <v>0.3572</v>
       </c>
       <c r="J109" t="n">
-        <v>11.841</v>
+        <v>10.716</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2551</v>
+        <v>-0.2162</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.653</v>
+        <v>-6.486</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.83</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5429</v>
+        <v>-0.5034</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.287</v>
+        <v>-15.102</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.96</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8626</v>
+        <v>0.8073</v>
       </c>
       <c r="J112" t="n">
-        <v>18.1146</v>
+        <v>16.9533</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.69</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6851</v>
+        <v>0.6415</v>
       </c>
       <c r="J113" t="n">
-        <v>14.3871</v>
+        <v>13.4715</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.65</v>
       </c>
       <c r="I114" t="n">
-        <v>0.658</v>
+        <v>0.6169</v>
       </c>
       <c r="J114" t="n">
-        <v>13.818</v>
+        <v>12.9549</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1462</v>
+        <v>0.1125</v>
       </c>
       <c r="J115" t="n">
-        <v>3.0702</v>
+        <v>2.3625</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0333</v>
+        <v>-0.0327</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.6993</v>
+        <v>-0.6867</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2871</v>
+        <v>0.296</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0291</v>
+        <v>6.216</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0102</v>
+        <v>0.0059</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.2142</v>
+        <v>0.1239</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4389</v>
+        <v>-0.431</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.216900000000001</v>
+        <v>-9.051</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5282</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.0607</v>
+        <v>-11.0922</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6481</v>
+        <v>-0.6693</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.6101</v>
+        <v>-14.0553</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3341</v>
+        <v>0.2811</v>
       </c>
       <c r="J122" t="n">
-        <v>8.352499999999999</v>
+        <v>7.0275</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2579</v>
+        <v>0.2106</v>
       </c>
       <c r="J123" t="n">
-        <v>6.4475</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0566</v>
+        <v>-0.0448</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.415</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1093</v>
+        <v>-0.0921</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.7325</v>
+        <v>-2.3025</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3266</v>
+        <v>-0.3101</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.164999999999999</v>
+        <v>-7.7525</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0084</v>
+        <v>0.9961</v>
       </c>
       <c r="J127" t="n">
-        <v>25.21</v>
+        <v>24.9025</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7135</v>
+        <v>0.6996</v>
       </c>
       <c r="J128" t="n">
-        <v>17.8375</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.3</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6691</v>
+        <v>0.6566</v>
       </c>
       <c r="J129" t="n">
-        <v>16.7275</v>
+        <v>16.415</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2078</v>
+        <v>-0.1736</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.195</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2702</v>
+        <v>-0.2322</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.755</v>
+        <v>-5.805</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.38</v>
       </c>
       <c r="I132" t="n">
-        <v>0.694</v>
+        <v>0.6353</v>
       </c>
       <c r="J132" t="n">
-        <v>20.82</v>
+        <v>19.059</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3641</v>
+        <v>0.3111</v>
       </c>
       <c r="J133" t="n">
-        <v>10.923</v>
+        <v>9.333</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3296</v>
+        <v>0.279</v>
       </c>
       <c r="J134" t="n">
-        <v>9.888</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0517</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.971</v>
+        <v>-1.551</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2409</v>
+        <v>-0.2211</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.227</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.17</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5119</v>
+        <v>0.4702</v>
       </c>
       <c r="J137" t="n">
-        <v>15.357</v>
+        <v>14.106</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3111</v>
+        <v>0.2707</v>
       </c>
       <c r="J138" t="n">
-        <v>9.333</v>
+        <v>8.121</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2269</v>
+        <v>0.1911</v>
       </c>
       <c r="J139" t="n">
-        <v>6.807</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3456</v>
+        <v>-0.3033</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.368</v>
+        <v>-9.099</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.423</v>
+        <v>-0.38</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.69</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.18</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3921</v>
+        <v>0.3363</v>
       </c>
       <c r="J142" t="n">
-        <v>11.763</v>
+        <v>10.089</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3921</v>
+        <v>0.3363</v>
       </c>
       <c r="J143" t="n">
-        <v>11.763</v>
+        <v>10.089</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0887</v>
+        <v>-0.0725</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.661</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0887</v>
+        <v>-0.0725</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.661</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1383</v>
+        <v>-0.1188</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.149</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.66</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3584</v>
+        <v>1.3886</v>
       </c>
       <c r="J147" t="n">
-        <v>40.752</v>
+        <v>41.658</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1902</v>
+        <v>0.1601</v>
       </c>
       <c r="J148" t="n">
-        <v>5.706</v>
+        <v>4.803</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0896</v>
+        <v>0.0708</v>
       </c>
       <c r="J149" t="n">
-        <v>2.688</v>
+        <v>2.124</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5322</v>
+        <v>-0.4914</v>
       </c>
       <c r="J150" t="n">
-        <v>-15.966</v>
+        <v>-14.742</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5793</v>
+        <v>-0.5403</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.379</v>
+        <v>-16.209</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4088</v>
+        <v>0.3523</v>
       </c>
       <c r="J152" t="n">
-        <v>12.264</v>
+        <v>10.569</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1865</v>
+        <v>0.1482</v>
       </c>
       <c r="J153" t="n">
-        <v>5.595</v>
+        <v>4.446</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1435</v>
+        <v>0.1112</v>
       </c>
       <c r="J154" t="n">
-        <v>4.305</v>
+        <v>3.336</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0275</v>
+        <v>-0.0195</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.825</v>
+        <v>-0.585</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1725</v>
+        <v>-0.152</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.175</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.35</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8862</v>
       </c>
       <c r="J157" t="n">
-        <v>27.081</v>
+        <v>26.586</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.09</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3086</v>
+        <v>0.2688</v>
       </c>
       <c r="J158" t="n">
-        <v>9.257999999999999</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2057</v>
+        <v>-0.1701</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.171</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4001</v>
+        <v>-0.357</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.003</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4001</v>
+        <v>-0.357</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.003</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6515</v>
+        <v>0.5998</v>
       </c>
       <c r="J162" t="n">
-        <v>16.939</v>
+        <v>15.5948</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1601</v>
+        <v>-0.1419</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.1626</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.83</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2119</v>
+        <v>-0.1923</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.5094</v>
+        <v>-4.9998</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.72</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3184</v>
+        <v>-0.3013</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.2784</v>
+        <v>-7.8338</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.762</v>
+        <v>-8.343400000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2413</v>
+        <v>1.2579</v>
       </c>
       <c r="J167" t="n">
-        <v>32.2738</v>
+        <v>32.7054</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.49</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0698</v>
+        <v>1.0795</v>
       </c>
       <c r="J168" t="n">
-        <v>27.8148</v>
+        <v>28.067</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5085</v>
+        <v>0.4783</v>
       </c>
       <c r="J169" t="n">
-        <v>13.221</v>
+        <v>12.4358</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.17</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4632</v>
+        <v>0.432</v>
       </c>
       <c r="J170" t="n">
-        <v>12.0432</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.09</v>
       </c>
       <c r="I171" t="n">
-        <v>0.2655</v>
+        <v>0.2345</v>
       </c>
       <c r="J171" t="n">
-        <v>6.903</v>
+        <v>6.097</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2181</v>
+        <v>0.1756</v>
       </c>
       <c r="J172" t="n">
-        <v>5.6706</v>
+        <v>4.5656</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0644</v>
+        <v>0.0455</v>
       </c>
       <c r="J173" t="n">
-        <v>1.6744</v>
+        <v>1.183</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.93</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1027</v>
+        <v>-0.0881</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.6702</v>
+        <v>-2.2906</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.2608</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.58</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4438</v>
+        <v>-0.437</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.5388</v>
+        <v>-11.362</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0209</v>
+        <v>1.0225</v>
       </c>
       <c r="J177" t="n">
-        <v>26.5434</v>
+        <v>26.585</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8219</v>
+        <v>0.8013</v>
       </c>
       <c r="J178" t="n">
-        <v>21.3694</v>
+        <v>20.8338</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.28</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7036</v>
+        <v>0.677</v>
       </c>
       <c r="J179" t="n">
-        <v>18.2936</v>
+        <v>17.602</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.21</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5603</v>
+        <v>0.5293</v>
       </c>
       <c r="J180" t="n">
-        <v>14.5678</v>
+        <v>13.7618</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.01</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0163</v>
+        <v>0.0062</v>
       </c>
       <c r="J181" t="n">
-        <v>0.4238</v>
+        <v>0.1612</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.95</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0168</v>
+        <v>0.9626</v>
       </c>
       <c r="J182" t="n">
-        <v>24.4032</v>
+        <v>23.1024</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.8</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8909</v>
+        <v>0.8214</v>
       </c>
       <c r="J183" t="n">
-        <v>21.3816</v>
+        <v>19.7136</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1994</v>
+        <v>0.1599</v>
       </c>
       <c r="J184" t="n">
-        <v>4.7856</v>
+        <v>3.8376</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0984</v>
+        <v>-0.0837</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.3616</v>
+        <v>-2.0088</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2065</v>
+        <v>-0.1886</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.956</v>
+        <v>-4.5264</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3991</v>
+        <v>0.408</v>
       </c>
       <c r="J187" t="n">
-        <v>9.5784</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0015</v>
+        <v>0.0089</v>
       </c>
       <c r="J188" t="n">
-        <v>0.036</v>
+        <v>0.2136</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3711</v>
+        <v>-0.3575</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.9064</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.58</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4336</v>
+        <v>-0.425</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4064</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.49</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5123</v>
+        <v>-0.5129</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.2952</v>
+        <v>-12.3096</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5758</v>
       </c>
       <c r="J192" t="n">
-        <v>22.176</v>
+        <v>20.153</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.403</v>
+        <v>0.3466</v>
       </c>
       <c r="J193" t="n">
-        <v>14.105</v>
+        <v>12.131</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3676</v>
+        <v>0.3128</v>
       </c>
       <c r="J194" t="n">
-        <v>12.866</v>
+        <v>10.948</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3277</v>
+        <v>-0.3114</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.4695</v>
+        <v>-10.899</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4878</v>
+        <v>-0.4876</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.073</v>
+        <v>-17.066</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9413</v>
+        <v>0.9282</v>
       </c>
       <c r="J197" t="n">
-        <v>32.9455</v>
+        <v>32.487</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4615</v>
+        <v>0.4246</v>
       </c>
       <c r="J198" t="n">
-        <v>16.1525</v>
+        <v>14.861</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4615</v>
+        <v>0.4246</v>
       </c>
       <c r="J199" t="n">
-        <v>16.1525</v>
+        <v>14.861</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.07</v>
       </c>
       <c r="I200" t="n">
-        <v>0.236</v>
+        <v>0.2053</v>
       </c>
       <c r="J200" t="n">
-        <v>8.26</v>
+        <v>7.1855</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0257</v>
+        <v>-0.0203</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.8995</v>
+        <v>-0.7105</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2073</v>
+        <v>1.2249</v>
       </c>
       <c r="J202" t="n">
-        <v>26.5606</v>
+        <v>26.9478</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.61</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2073</v>
+        <v>1.2249</v>
       </c>
       <c r="J203" t="n">
-        <v>26.5606</v>
+        <v>26.9478</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9304</v>
+        <v>0.927</v>
       </c>
       <c r="J204" t="n">
-        <v>20.4688</v>
+        <v>20.394</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8758</v>
+        <v>0.8679</v>
       </c>
       <c r="J205" t="n">
-        <v>19.2676</v>
+        <v>19.0938</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.21</v>
       </c>
       <c r="I206" t="n">
-        <v>0.5331</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>11.7282</v>
+        <v>11.121</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.04</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2093</v>
+        <v>0.1824</v>
       </c>
       <c r="J207" t="n">
-        <v>4.6046</v>
+        <v>4.0128</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.77</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2543</v>
+        <v>-0.2396</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.5946</v>
+        <v>-5.2712</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.7</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3183</v>
+        <v>-0.3042</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.0026</v>
+        <v>-6.6924</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.58</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4251</v>
+        <v>-0.4159</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.3522</v>
+        <v>-9.149800000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5228</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.4774</v>
+        <v>-11.5016</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.91</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1076</v>
+        <v>-0.0927</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.3672</v>
+        <v>-2.0394</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.85</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1767</v>
+        <v>-0.1611</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.8874</v>
+        <v>-3.5442</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.7</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3212</v>
+        <v>-0.3061</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.0664</v>
+        <v>-6.7342</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.63</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3843</v>
+        <v>-0.3719</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.454599999999999</v>
+        <v>-8.181800000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3932</v>
+        <v>-0.3814</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.650399999999999</v>
+        <v>-8.3908</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.64</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7328</v>
+        <v>0.6616</v>
       </c>
       <c r="J217" t="n">
-        <v>16.1216</v>
+        <v>14.5552</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.58</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6763</v>
+        <v>0.6058</v>
       </c>
       <c r="J218" t="n">
-        <v>14.8786</v>
+        <v>13.3276</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.49</v>
       </c>
       <c r="I219" t="n">
-        <v>0.59</v>
+        <v>0.5221</v>
       </c>
       <c r="J219" t="n">
-        <v>12.98</v>
+        <v>11.4862</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.21</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2949</v>
+        <v>0.246</v>
       </c>
       <c r="J220" t="n">
-        <v>6.4878</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.2199</v>
+        <v>0.1781</v>
       </c>
       <c r="J221" t="n">
-        <v>4.8378</v>
+        <v>3.9182</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1792</v>
+        <v>1.1968</v>
       </c>
       <c r="J222" t="n">
-        <v>24.7632</v>
+        <v>25.1328</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0236</v>
+        <v>1.0334</v>
       </c>
       <c r="J223" t="n">
-        <v>21.4956</v>
+        <v>21.7014</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.46</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0093</v>
+        <v>1.0171</v>
       </c>
       <c r="J224" t="n">
-        <v>21.1953</v>
+        <v>21.3591</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9785</v>
+        <v>0.9822</v>
       </c>
       <c r="J225" t="n">
-        <v>20.5485</v>
+        <v>20.6262</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.38</v>
       </c>
       <c r="I226" t="n">
-        <v>0.8729</v>
+        <v>0.8657</v>
       </c>
       <c r="J226" t="n">
-        <v>18.3309</v>
+        <v>18.1797</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.86</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1402</v>
+        <v>-0.1213</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.9442</v>
+        <v>-2.5473</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.73</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2794</v>
+        <v>-0.2669</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.8674</v>
+        <v>-5.6049</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3631</v>
+        <v>-0.3531</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.6251</v>
+        <v>-7.4151</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.51</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4754</v>
+        <v>-0.4711</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.9834</v>
+        <v>-9.8931</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.4</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5722</v>
+        <v>-0.5795</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.0162</v>
+        <v>-12.1695</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0694</v>
+        <v>1.0776</v>
       </c>
       <c r="J232" t="n">
-        <v>27.8044</v>
+        <v>28.0176</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.42</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9918</v>
+        <v>0.9871</v>
       </c>
       <c r="J233" t="n">
-        <v>25.7868</v>
+        <v>25.6646</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5268</v>
+        <v>0.4908</v>
       </c>
       <c r="J234" t="n">
-        <v>13.6968</v>
+        <v>12.7608</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3475</v>
+        <v>-0.3061</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.035</v>
+        <v>-7.9586</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5016</v>
+        <v>-0.4615</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.0416</v>
+        <v>-11.999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3976</v>
+        <v>0.3421</v>
       </c>
       <c r="J237" t="n">
-        <v>10.3376</v>
+        <v>8.894600000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.13</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3241</v>
+        <v>0.272</v>
       </c>
       <c r="J238" t="n">
-        <v>8.426600000000001</v>
+        <v>7.072</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.86</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1852</v>
+        <v>-0.1652</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.8152</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2163</v>
+        <v>-0.196</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.6238</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.351</v>
+        <v>-0.336</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.125999999999999</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1444</v>
+        <v>1.1573</v>
       </c>
       <c r="J242" t="n">
-        <v>30.8988</v>
+        <v>31.2471</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8519</v>
+        <v>0.8312</v>
       </c>
       <c r="J243" t="n">
-        <v>23.0013</v>
+        <v>22.4424</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3852</v>
+        <v>0.3511</v>
       </c>
       <c r="J244" t="n">
-        <v>10.4004</v>
+        <v>9.479699999999999</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1035</v>
+        <v>0.083</v>
       </c>
       <c r="J245" t="n">
-        <v>2.7945</v>
+        <v>2.241</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.98</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1356</v>
+        <v>-0.1084</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.6612</v>
+        <v>-2.9268</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2505</v>
+        <v>0.204</v>
       </c>
       <c r="J247" t="n">
-        <v>6.7635</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2505</v>
+        <v>0.204</v>
       </c>
       <c r="J248" t="n">
-        <v>6.7635</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1059</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.8593</v>
+        <v>-2.4381</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2346</v>
+        <v>-0.2146</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.3342</v>
+        <v>-5.7942</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3763</v>
+        <v>-0.3632</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1601</v>
+        <v>-9.8064</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.96</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0473</v>
+        <v>-0.0361</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.0406</v>
+        <v>-0.7942</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.88</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1485</v>
+        <v>-0.133</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.267</v>
+        <v>-2.926</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2787</v>
+        <v>-0.262</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.1314</v>
+        <v>-5.764</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2787</v>
+        <v>-0.262</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.1314</v>
+        <v>-5.764</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.53</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4766</v>
+        <v>-0.4726</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.4852</v>
+        <v>-10.3972</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.52</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6283</v>
+        <v>0.5575</v>
       </c>
       <c r="J257" t="n">
-        <v>13.8226</v>
+        <v>12.265</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.47</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5787</v>
+        <v>0.5093</v>
       </c>
       <c r="J258" t="n">
-        <v>12.7314</v>
+        <v>11.2046</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.44</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5486</v>
+        <v>0.4804</v>
       </c>
       <c r="J259" t="n">
-        <v>12.0692</v>
+        <v>10.5688</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2145</v>
+        <v>0.1733</v>
       </c>
       <c r="J260" t="n">
-        <v>4.719</v>
+        <v>3.8126</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0644</v>
+        <v>0.045</v>
       </c>
       <c r="J261" t="n">
-        <v>1.4168</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.84</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5345</v>
+        <v>1.5717</v>
       </c>
       <c r="J262" t="n">
-        <v>44.5005</v>
+        <v>45.5793</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6841</v>
+        <v>0.6565</v>
       </c>
       <c r="J263" t="n">
-        <v>19.8389</v>
+        <v>19.0385</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.26</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6641</v>
+        <v>0.6358</v>
       </c>
       <c r="J264" t="n">
-        <v>19.2589</v>
+        <v>18.4382</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.1</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3014</v>
+        <v>0.2696</v>
       </c>
       <c r="J265" t="n">
-        <v>8.740600000000001</v>
+        <v>7.8184</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6341</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.3889</v>
+        <v>-17.4667</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.47</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8972</v>
+        <v>0.8619</v>
       </c>
       <c r="J267" t="n">
-        <v>26.0188</v>
+        <v>24.9951</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1282</v>
+        <v>-0.1114</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.7178</v>
+        <v>-3.2306</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1819</v>
+        <v>-0.1627</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.2751</v>
+        <v>-4.7183</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.338</v>
+        <v>-0.322</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.802</v>
+        <v>-9.337999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4719</v>
+        <v>-0.4685</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.6851</v>
+        <v>-13.5865</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.06</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8009</v>
+        <v>1.8675</v>
       </c>
       <c r="J272" t="n">
-        <v>45.0225</v>
+        <v>46.6875</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.35</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8403</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J273" t="n">
-        <v>21.0075</v>
+        <v>20.5275</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.12</v>
       </c>
       <c r="I274" t="n">
-        <v>0.351</v>
+        <v>0.3185</v>
       </c>
       <c r="J274" t="n">
-        <v>8.775</v>
+        <v>7.9625</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.02</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0567</v>
+        <v>0.0403</v>
       </c>
       <c r="J275" t="n">
-        <v>1.4175</v>
+        <v>1.0075</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.77</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7033</v>
+        <v>-0.6766</v>
       </c>
       <c r="J276" t="n">
-        <v>-17.5825</v>
+        <v>-16.915</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.15</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J277" t="n">
-        <v>9.1425</v>
+        <v>7.795</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.08</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2287</v>
+        <v>0.1842</v>
       </c>
       <c r="J278" t="n">
-        <v>5.7175</v>
+        <v>4.605</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1624</v>
+        <v>-0.1433</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.06</v>
+        <v>-3.5825</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.595</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4037</v>
+        <v>-0.393</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.0925</v>
+        <v>-9.824999999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.91</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5611</v>
+        <v>1.5971</v>
       </c>
       <c r="J282" t="n">
-        <v>29.6609</v>
+        <v>30.3449</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.69</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2978</v>
+        <v>1.3196</v>
       </c>
       <c r="J283" t="n">
-        <v>24.6582</v>
+        <v>25.0724</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.61</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1994</v>
+        <v>1.2186</v>
       </c>
       <c r="J284" t="n">
-        <v>22.7886</v>
+        <v>23.1534</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.41</v>
       </c>
       <c r="I285" t="n">
-        <v>0.9227</v>
+        <v>0.9214</v>
       </c>
       <c r="J285" t="n">
-        <v>17.5313</v>
+        <v>17.5066</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.315</v>
+        <v>-0.2853</v>
       </c>
       <c r="J286" t="n">
-        <v>-5.985</v>
+        <v>-5.4207</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.92</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0737</v>
+        <v>-0.055</v>
       </c>
       <c r="J287" t="n">
-        <v>-1.4003</v>
+        <v>-1.045</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0866</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.6454</v>
+        <v>-1.2939</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3999</v>
+        <v>-0.39</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.5981</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.54</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4527</v>
+        <v>-0.4462</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.6013</v>
+        <v>-8.4778</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.3</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6625</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.5875</v>
+        <v>-13.034</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.6376</v>
+        <v>1.6801</v>
       </c>
       <c r="J292" t="n">
-        <v>31.1144</v>
+        <v>31.9219</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.84</v>
       </c>
       <c r="I293" t="n">
-        <v>1.4646</v>
+        <v>1.4958</v>
       </c>
       <c r="J293" t="n">
-        <v>27.8274</v>
+        <v>28.4202</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.7</v>
       </c>
       <c r="I294" t="n">
-        <v>1.2994</v>
+        <v>1.3238</v>
       </c>
       <c r="J294" t="n">
-        <v>24.6886</v>
+        <v>25.1522</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.46</v>
       </c>
       <c r="I295" t="n">
-        <v>0.996</v>
+        <v>1.0071</v>
       </c>
       <c r="J295" t="n">
-        <v>18.924</v>
+        <v>19.1349</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1086</v>
+        <v>0.0759</v>
       </c>
       <c r="J296" t="n">
-        <v>2.0634</v>
+        <v>1.4421</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.73</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.2591</v>
+        <v>-0.2444</v>
       </c>
       <c r="J297" t="n">
-        <v>-4.9229</v>
+        <v>-4.6436</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.64</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3495</v>
+        <v>-0.3415</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.6405</v>
+        <v>-6.4885</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.63</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.359</v>
+        <v>-0.3516</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.821</v>
+        <v>-6.6804</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5856</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.9839</v>
+        <v>-11.1264</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.596</v>
+        <v>-0.6061</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.324</v>
+        <v>-11.5159</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.41</v>
       </c>
       <c r="I302" t="n">
-        <v>0.975</v>
+        <v>0.9674</v>
       </c>
       <c r="J302" t="n">
-        <v>34.125</v>
+        <v>33.859</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.39</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9387</v>
+        <v>0.9254</v>
       </c>
       <c r="J303" t="n">
-        <v>32.8545</v>
+        <v>32.389</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.2</v>
       </c>
       <c r="I304" t="n">
-        <v>0.549</v>
+        <v>0.5131</v>
       </c>
       <c r="J304" t="n">
-        <v>19.215</v>
+        <v>17.9585</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1654</v>
+        <v>-0.1339</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.789</v>
+        <v>-4.6865</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.86</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4767</v>
+        <v>-0.4358</v>
       </c>
       <c r="J306" t="n">
-        <v>-16.6845</v>
+        <v>-15.253</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.51</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9266</v>
+        <v>0.8878</v>
       </c>
       <c r="J307" t="n">
-        <v>32.431</v>
+        <v>31.073</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.99</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0233</v>
+        <v>-0.0172</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.8155</v>
+        <v>-0.602</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.92</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1207</v>
+        <v>-0.1029</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.2245</v>
+        <v>-3.6015</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.8</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2491</v>
+        <v>-0.2291</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.718500000000001</v>
+        <v>-8.0185</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4342</v>
+        <v>-0.4272</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.197</v>
+        <v>-14.952</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.38</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9197</v>
+        <v>0.904</v>
       </c>
       <c r="J312" t="n">
-        <v>25.7516</v>
+        <v>25.312</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6772</v>
+        <v>0.645</v>
       </c>
       <c r="J313" t="n">
-        <v>18.9616</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.25</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6562</v>
+        <v>0.6231</v>
       </c>
       <c r="J314" t="n">
-        <v>18.3736</v>
+        <v>17.4468</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3156</v>
+        <v>0.2818</v>
       </c>
       <c r="J315" t="n">
-        <v>8.8368</v>
+        <v>7.8904</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5255</v>
+        <v>-0.4861</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.714</v>
+        <v>-13.6108</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4826</v>
+        <v>0.425</v>
       </c>
       <c r="J317" t="n">
-        <v>13.5128</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.16</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3775</v>
+        <v>0.3225</v>
       </c>
       <c r="J318" t="n">
-        <v>10.57</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1192</v>
+        <v>-0.1019</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.3376</v>
+        <v>-2.8532</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2372</v>
+        <v>-0.2171</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.6416</v>
+        <v>-6.0788</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4236</v>
+        <v>-0.4152</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.8608</v>
+        <v>-11.6256</v>
       </c>
     </row>
   </sheetData>
